--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0015.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0015.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đây là lần quan sát thứ ███ tại Tacet Field HL-057, do Máy Quan sát Tự động 11371A thực hiện.
+          <t xml:space="preserve">Đây là lần quan sát thứ ███ tại Tổ Tacet HL-057, do Máy Quan sát Tự động 11371A thực hiện.
 </t>
         </is>
       </c>
@@ -709,7 +709,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retrieving visual environment...
+          <t xml:space="preserve">Đang truy xuất môi trường hình ảnh...
 </t>
         </is>
       </c>
@@ -1444,8 +1444,8 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>Một món đồ chơi được chế tác từ những khớp nối phức tạp, tinh xảo, minh chứng cho thiết kế tài tình. Người ta kể rằng những món đồ như vậy từng là quà tặng của các bậc trưởng lão tại Tòa án Savantae dành cho thế hệ trẻ.
-Tưởng Lệ Yao vẫn còn nhớ cảm giác ấm áp từ những đầu ngón tay thô ráp của cha khi ông trao cho cậu món đồ chơi vào ngày sinh nhật. Nhưng điều thực sự khiến cậu say mê chính là những cấu trúc phức tạp, bí ẩn của nó—những câu đố như vậy đã đưa cậu vào thế giới logic phức tạp, khiến cậu mê mẩn suốt bao năm qua.
-Đây là lần đầu Tưởng Lệ Yao tiếp xúc với một câu đố, nhưng chắc chắn không phải lần cuối.</t>
+Tưởng Lệ Dao vẫn còn nhớ cảm giác ấm áp từ những đầu ngón tay thô ráp của cha khi ông trao cho cậu món đồ chơi vào ngày sinh nhật. Nhưng điều thực sự khiến cậu say mê chính là những cấu trúc phức tạp, bí ẩn của nó—những câu đố như vậy đã đưa cậu vào thế giới logic phức tạp, khiến cậu mê mẩn suốt bao năm qua.
+Đây là lần đầu Tưởng Lệ Dao tiếp xúc với một câu đố, nhưng chắc chắn không phải lần cuối.</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>Cô bé hãnh diện đưa bức tranh của mình cho mẹ, háo hức muốn chia sẻ thành quả. Người phụ nữ đang mải mê chọn đồ trang sức, chỉ liếc qua bức tranh một cách thoáng qua. "Tuyệt lắm, Zhezhi," bà thì thầm với nụ cười gượng gạo. Vui mừng vì lời khen, cô bé tiến lại gần hơn. "Những người trong bức này—" Lời cô bé đứt quãng khi mẹ quay đi, vẫn chăm chú vào việc lựa chọn trang phục, không hề để ý đến nỗ lực kết nối của con gái. "Làm tốt lắm. Sao con không vẽ thêm vài bức nữa trước khi khách đến?" Zhezhi chớp mắt, không biết nói gì. Mẹ cô sốt ruột, thở dài rồi đẩy cô ra cửa. "Muốn mua gì thì mua, con yêu. Tiền bạc không thành vấn đề, nhà mình đủ khả năng mà. Giờ mẹ phải thay đồ. Ngoan nhé. Đi đi." Khi cánh cửa đóng lại, Zhezhi nhìn chằm chằm vào đó, muốn nói thêm gì đó nhưng không đủ can đảm để thốt ra nỗi buồn đang dâng lên trong lòng.
-Tối hôm đó, Zhezhi diện đồ đẹp, ngồi co ro ở góc phòng, tay nắm chặt váy, im lặng giữa không gian tấp nập của khách khứa. Người phụ nữ nhận thấy sự bất an của Zhezhi, cảnh tượng ấy gợi lại ký ức về những ngày tháng cơ cực trước kia của gia đình. Bà bước tới, nắm tay Zhezhi và dẫn cô vào trung tâm sự chú ý. "Các vị không biết sao? Zhezhi đã là thiên tài từ khi mới sinh ra. Tranh của con bé được chọn triển lãm từ trước khi chúng ta thuê gia sư đấy." Với nụ cười giả tạo, bà bắt chước phong thái của giới thượng lưu. "Quý vị có muốn sở hữu một bức tranh không? Zhezhi có thể hoàn thành trong một ngày." Zhezhi co rúm người lại, chỉ muốn biến mất, nhưng lại bị đẩy ra trước. "Thể hiện tài năng của con đi, Zhezhi." Mọi ánh mắt đổ dồn về cô, khiến Zhezhi run rẩy, không thể vẽ nổi một Dodget.
+Tối hôm đó, Zhezhi diện đồ đẹp, ngồi co ro ở góc phòng, tay nắm chặt váy, im lặng giữa không gian tấp nập của khách khứa. Người phụ nữ nhận thấy sự bất an của Zhezhi, cảnh tượng ấy gợi lại ký ức về những ngày tháng cơ cực trước kia của gia đình. Bà bước tới, nắm tay Zhezhi và dẫn cô vào trung tâm sự chú ý. "Các vị không biết sao? Zhezhi đã là thiên tài từ khi mới sinh ra. Tranh của con bé được chọn triển lãm từ trước khi chúng ta thuê gia sư đấy." Với nụ cười giả tạo, bà bắt chước phong thái của giới thượng lưu. "Quý vị có muốn sở hữu một bức tranh không? Zhezhi có thể hoàn thành trong một ngày." Zhezhi co rúm người lại, chỉ muốn biến mất, nhưng lại bị đẩy ra trước. "Thể hiện tài năng của con đi, Zhezhi." Mọi ánh mắt đổ dồn về cô, khiến Zhezhi run rẩy, không thể vẽ nổi một nét.
 Sau đó, khi biệt thự chìm vào im lặng, Zhezhi lại lấy hết can đảm. Tay cầm bức tranh vẽ trong ngày, cô tiến đến cửa phòng ngủ của bố mẹ. Ngay trước khi gõ cửa, cô nghe thấy cuộc trò chuyện bên trong.
 "Em biết không? Bức tranh đó hôm nay bán được 400.000 Credits đấy. Với số tiền này, chúng ta có thể hoàn tất đơn hàng bị hoãn rồi."
 "Ừ. Tranh cho khách cuối tuần đã xong chưa?"
@@ -1682,7 +1682,7 @@
 Quãng đường từ giàu sang xuống tận cùng khổ sở dường như kéo dài vô tận, mỗi ngày là một nhắc nhở đau đớn. Những con số nợ khổng lồ của cha mẹ cô như lởn vởn trên trần nhà trong ánh sáng lờ mờ của căn phòng không cửa sổ. Đôi tay băng bó sờn rách run rẩy sau hai ngày vẽ không ngừng, nhưng cô không dám nghỉ.
 "Đơn hàng lớn thế này... Không được phép làm hỏng," cô thì thầm, đôi mắt mệt mỏi làm mờ đi những phong cảnh trên bức tranh.
 Bỗng nhiên, tiếng la hét chói tai xuyên đêm đánh thức cô khỏi giấc ngủ gật trên bàn. Cô loạng choạng đứng dậy, trượt chân trên thứ gì đó ướt át dưới chân.
-Đau đớn vì ngã, cô đứng run rẩy trước cửa phòng bị dột, liên tục xin lỗi hàng xóm. Cái lạnh thấu xương thấm qua quần áo ướt, tiếng phàn nàn của họ vọng qua những bức tường mỏng. Cô nhìn bức tranh bị nước hủy hoại, một tiếng thở dài nặng nề thoát ra, như Dodgen chặt không khí mỏng manh trong phòng, suýt nữa nghiền nát thân hình yếu ớt của cô.
+Đau đớn vì ngã, cô đứng run rẩy trước cửa phòng bị dột, liên tục xin lỗi hàng xóm. Cái lạnh thấu xương thấm qua quần áo ướt, tiếng phàn nàn của họ vọng qua những bức tường mỏng. Cô nhìn bức tranh bị nước hủy hoại, một tiếng thở dài nặng nề thoát ra, như nén chặt không khí mỏng manh trong phòng, suýt nữa nghiền nát thân hình yếu ớt của cô.
 Dáng vẻ kiệt sức của Zhezhi đứng bất động trong vũng nước lạnh. Sau một hồi lâu, một ánh sáng le lói xuất hiện trong căn phòng chật hẹp. Bằng những đầu ngón tay dính đầy sơn, cô lướt trên Terminal, "Đầu tiên, khóa van nước... rồi thay thế các bộ phận hỏng..."
 Cô đã quen với việc tìm kiếm giải pháp cho những khó khăn bất ngờ trong cuộc sống.
 "Chắc là được... Để ta thử xem..."
@@ -1780,8 +1780,8 @@
 "Có người khen mình... "
 "Họ chẳng được lợi gì từ việc đó. Chỉ là... lời khen đơn thuần cho tranh của mình thôi."
 Lời của người lạ, đơn giản mà chân thành, xuyên qua những bức tranh để chạm đến trái tim cô. Lần đầu tiên, có ai đó thực sự hiểu được ý đồ sáng tạo của cô. Như một tia sáng đột ngột xua tan đám mây u ám đã đè nặng cô bấy lâu, mang lại hơi ấm mà cô chưa từng cảm nhận.
-Zhezhi nhìn theo hướng người lạ đã biến mất, ôm chặt những bức tranh vào lòng. Until...
-"Xin lỗi... Hello?"
+Zhezhi nhìn theo hướng người lạ đã biến mất, ôm chặt những bức tranh vào lòng. Cho đến khi...
+"Xin lỗi... Xin chào?"
 Vài ngày sau, một giọng nói quen thuộc khiến cô giật mình khỏi dòng suy nghĩ khi đang tìm địa điểm vẽ tranh hoàn hảo.
 "Đừng lo, chúng ta chỉ đến để trò chuyện thôi."
 Zhezhi ngước lên và nhìn thấy đôi mắt vàng. Ký ức về đêm đó ùa về—đây chính là người đã khen ngợi tác phẩm của cô, giọng nói không chút giả tạo như những lời cô từng nghe từ người khác. Chính giọng nói đó đã tiếp thêm sức mạnh cho cô khi cô sắp buông xuôi tất cả.
@@ -3937,8 +3937,8 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Một Discord độc nhất. Gulpuff này sinh ra từ dữ liệu dị thường, sở hữu kích thước khổng lồ và sức hủy diệt đáng sợ.
-Dù Gulpuff thường được xếp vào loại Discord Common, con này đã có được khả năng chiến đấu vượt trội và tính khí hung dữ do ảnh hưởng của dữ liệu dị thường. Giữ khoảng cách an toàn là điều nên làm.</t>
+          <t>Một Tacet Discord độc nhất. Gulpuff này sinh ra từ dữ liệu dị thường, sở hữu kích thước khổng lồ và sức hủy diệt đáng sợ.
+Dù Gulpuff thường được xếp vào loại Tacet Discord Thường, con này đã có được khả năng chiến đấu vượt trội và tính khí hung dữ do ảnh hưởng của dữ liệu dị thường. Giữ khoảng cách an toàn là điều nên làm.</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Echo Độc Nhất. Một đàn Cruisewing tụ tập do dữ liệu dị thường, thể hiện mức độ phối hợp nhất định.
+          <t>Tổ Tacet Độc Nhất. Một đàn Cruisewing tụ tập do dữ liệu dị thường, thể hiện mức độ phối hợp nhất định.
 Dù từng cá thể Cruisewing yếu ớt, sức mạnh tập thể của chúng có thể tạo nên một cơn bão khủng khiếp.
 Đừng bao giờ đánh giá thấp sức chiến đấu của đàn này.</t>
         </is>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Một Discord độc nhất. Chiến binh Fusion này sinh ra từ dữ liệu dị thường, sở hữu kỹ năng chiến đấu vượt xa tưởng tượng.
+          <t>Một Tacet Discord độc nhất. Chiến binh Fusion này sinh ra từ dữ liệu dị thường, sở hữu kỹ năng chiến đấu vượt xa tưởng tượng.
 Hai lưỡi kiếm thay thế đôi tay của nó dường như có tri giác, khai thác mọi sơ hở trong tư thế đối thủ.
 Tần số cụ thể mà nó bắt chước để đạt đến trình độ kiếm thuật như vậy vẫn còn là bí ẩn.</t>
         </is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Một Discord độc nhất. Rocksteady Guardian này sinh ra từ dữ liệu dị thường, có thể đập vỡ nhiều lớp đá chỉ bằng một cú đánh.
+          <t>Một Tacet Discord độc nhất. Rocksteady Guardian này sinh ra từ dữ liệu dị thường, có thể đập vỡ nhiều lớp đá chỉ bằng một cú đánh.
 Dù di chuyển chậm chạp, sức mạnh hủy diệt của nó hoàn toàn bù đắp được điều đó.
 Sức mạnh thô bạo, đơn giản và thuần túy.</t>
         </is>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Echo Độc Nhất. Hai Tambourinist hợp nhất do dữ liệu dị thường, sở hữu tần số với cường độ không thể tưởng tượng.
+          <t>Tổ Tacet Độc Nhất. Hai Tambourinist hợp nhất do dữ liệu dị thường, sở hữu tần số với cường độ không thể tưởng tượng.
 Âm thanh từ nhạc cụ của chúng như những tiếng gào thét và oán hận từ vực thẳm—kinh hoàng đến mức chỉ cần nghe thấy cũng có thể mang lại vận rủi.</t>
         </is>
       </c>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Hành trình của cậu bắt đầu tại Jinzhou. Nhưng những bí ẩn gần đây đã dẫn cậu đến một quần đảo chìm trong sương mù—Black Shores. Có lẽ nơi cô độc này sẽ là điểm dừng chân cuối cùng của cậu...</t>
+          <t>Hành trình của cậu bắt đầu tại Jinzhou. Nhưng những bí ẩn gần đây đã dẫn cậu đến một quần đảo chìm trong sương mù—Bờ Biển Đen. Có lẽ nơi cô độc này sẽ là điểm dừng chân cuối cùng của cậu...</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>The Black Shores ẩn mình trên một hòn đảo bị sương mù biển dày đặc bao phủ—nơi trú ẩn an toàn cho vô số Tư Vấn Viên và Người Mang Hoa lang thang khắp thế giới. Nếu không có lời mời từ các thành viên, chưa ai từng tìm ra được con tàu nổi kết nối thế giới giữa đại dương mênh mông này…</t>
+          <t>Bờ Biển Đen ẩn mình trên một hòn đảo bị sương mù biển dày đặc bao phủ—nơi trú ẩn an toàn cho vô số Tư Vấn Viên và Người Mang Hoa lang thang khắp thế giới. Nếu không có lời mời từ các thành viên, chưa ai từng tìm ra được con tàu nổi kết nối thế giới giữa đại dương mênh mông này…</t>
         </is>
       </c>
     </row>
@@ -5881,11 +5881,11 @@
 Nền văn minh sụp đổ thành tro bụi rồi lại hồi sinh; sự sống tàn lụi rồi lại nở rộ.
 Nàng chứng kiến sự thăng trầm của Solaris, nhưng trong tâm trí mình, nàng mãi là kẻ lang thang.
 "{PlayerName}…" Cái tên tuôn ra khỏi môi như một lời cầu nguyện.
-Họ chưa từng thực sự gặp gỡ hay trò chuyện, và giờ đây, khi ký ức phai mờ, nàng thậm chí không biết họ là bạn hay thù. Nhưng kỳ lạ thay, lần tỉnh dậy sau, bản năng sẽ lại thôi thúc nàng tìm đến {Male=chàng;Female=nàng}. Đó không phải là khao khát dịu dàng. Nó giống như sức nặng của một sợi xích nặng trĩu, mà Quý cô Flora không thể cưỡng lại.
+Họ chưa từng thực sự gặp gỡ hay trò chuyện, và giờ đây, khi ký ức phai mờ, nàng thậm chí không biết họ là bạn hay thù. Nhưng kỳ lạ thay, lần tỉnh dậy sau, bản năng sẽ lại thôi thúc nàng tìm đến {Male=him;Female=her}. Đó không phải là khao khát dịu dàng. Nó giống như sức nặng của một sợi xích nặng trĩu, mà Quý cô Flora không thể cưỡng lại.
 Nhưng nàng không hề căm ghét sợi xích ấy.
 Tiếng lá xào xạc kéo nàng khỏi cơn mơ màng. Mệt mỏi, nàng chớp mắt, và đóa hoa trà đỏ bung nở, những sợi dây leo đâm xuyên qua những &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; ẩn nấp trong bóng tối. Đúng vậy, đây là bản năng, là bản chất, là cốt lõi của nàng… Dù đứng bên bờ vực quên lãng, nàng vẫn luôn có thể tin vào bản năng của mình.
 Thực ra, ngoài bản năng, nàng chẳng còn gì để bám víu.
-"Lần sau, giá như ta có thể thực sự hiểu {PlayerName} và trò chuyện với {Male=chàng;Female=nàng}."
+"Lần sau, giá như ta có thể thực sự hiểu {PlayerName} và trò chuyện với {Male=him;Female=her}."
 Quý cô Flora mơ màng nghĩ. Có lẽ &lt;te href=850110&gt;Hệ thống Tethys&lt;/te&gt; sẽ dẫn {PlayerName} đến với nàng, vì nàng đã tự lộ diện trong nhiệm vụ này.
 Quý cô Flora nhắm mắt, đầu hàng bóng tối khi cơn đau lên đến đỉnh điểm.
 Nước hồ mát lạnh dâng lên gò má, đóa hoa trà héo úa khi những sợi dây leo thu mình trở lại cơ thể.
@@ -7519,7 +7519,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Searching......]
+          <t xml:space="preserve">["Đang tìm kiếm......"]
 </t>
         </is>
       </c>
@@ -7938,8 +7938,8 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Magistrate Jinhsi nhất quyết bảo ta nghỉ ngơi đôi chút. Đêm nay phố phường nhộn nhịp lạ thường. Vì chẳng có việc gì làm, ta đã nhấm nháp chút... trà hoa. Người thì ấm áp, lòng lại khát khao có ai đó để giãi bày.
-Người dân nơi đây thường đeo mặt nạ quái vật trong các điệu múa nghi lễ. Họ tin rằng việc tái hiện lại những con quái vật trong truyền thuyết Huanglong có thể xua đuổi tà ma, mang lại may mắn. Còn ta... ta chẳng cần tái hiện đâu, bởi ta đã nỗ lực kìm Dodgen con quái vật bên trong, và đó chính là chiếc mặt nạ hoàn hảo nhất của ta.
+          <t>Quan Án Jinhsi nhất quyết bảo ta nghỉ ngơi đôi chút. Đêm nay phố phường nhộn nhịp lạ thường. Vì chẳng có việc gì làm, ta đã nhấm nháp chút... trà hoa. Người thì ấm áp, lòng lại khát khao có ai đó để giãi bày.
+Người dân nơi đây thường đeo mặt nạ quái vật trong các điệu múa nghi lễ. Họ tin rằng việc tái hiện lại những con quái vật trong truyền thuyết Huanglong có thể xua đuổi tà ma, mang lại may mắn. Còn ta... ta chẳng cần tái hiện đâu, bởi ta đã nỗ lực kìm nén con quái vật bên trong, và đó chính là chiếc mặt nạ hoàn hảo nhất của ta.
 Những âm thanh, hình ảnh kỳ lạ trong gió tuyết lạnh lẽo ấy là quá khứ mà ta không thể cắt đứt. Nhưng nhờ có các người, ta mới thấy được tia hy vọng sau những cảnh tượng u ám này. Các người đã cho ta sức mạnh để cầu nguyện cho mùa xuân trở lại.
 Số phận mà các người gieo trồng sẽ đơm hoa kết trái trong những năm tới. Nếu các người lại lên đường, xin hãy nhớ mang theo... lời chúc phúc của ta và của mọi người nhé.
 Sanhua</t>
@@ -8014,7 +8014,7 @@
           <t>Năm nay, buổi lễ khác hẳn—đây là lần đầu tiên không còn bóng dáng của mối đe dọa Threnody. Mọi người cuối cùng cũng có thể cười vui từ đáy lòng, và tôi thật sự thích nhìn thấy nụ cười của tất cả mọi người.
 Tôi đã bảo Sanhua và Taoqi nghỉ ngơi. Sau cả năm làm việc, họ xứng đáng được tận hưởng khoảng thời gian thư giãn này, đắm chìm trong hơi ấm khó khăn lắm mới có được. Khi thấy mọi người sum vầy bên gia đình, tôi không khỏi mong mỏi có anh ở đây. Tôi biết anh có việc phải làm, nhưng sự vắng mặt của anh trong những ngày lễ tưng bừng nhất năm này hẳn sẽ khiến mọi người cảm thấy cô đơn đôi chút.
 Vậy nên, khi anh trở về cùng những vị khách từ Rinascita, tôi thật sự vui mừng—anh quả thật nhớ Jinzhou đến mức dành thời gian ở bên tôi. Có lẽ, trong lòng anh, Jinzhou đã trở thành quê hương.
-Tôi đã viết một bài hát để bày tỏ lòng biết ơn, và có vẻ cuối cùng tôi cũng sẽ được hát nó. Wear bộ lễ phục này vẫn khiến tôi hơi ngại, nhưng nếu anh thích, sau khi xong việc, tôi sẽ mặc chỉnh tề và hát riêng cho anh nghe.
+Tôi đã viết một bài hát để bày tỏ lòng biết ơn, và có vẻ cuối cùng tôi cũng sẽ được hát nó. Mặc bộ lễ phục này vẫn khiến tôi hơi ngại, nhưng nếu anh thích, sau khi xong việc, tôi sẽ mặc chỉnh tề và hát riêng cho anh nghe.
 Jinhsi</t>
         </is>
       </c>
@@ -8163,10 +8163,10 @@
       <c r="M115" t="inlineStr">
         <is>
           <t>("Một bức thư viết tay ngay ngắn với chữ ký nguệch ngoạc)
-Hừm, đây là thư ta viết cho ngươi đấy. Ngạc nhiên không? Ta cũng vậy. Ý ta là, nếu ta có gì muốn nói, ta có thể nói thẳng với ngươi mà, phải không? Nhưng thấy mọi người đều viết thư nên ta nhờ Sanhua ghi lại những gì ta nói.
+Hừm, đây là thư tao viết cho mày đấy. Ngạc nhiên không? Tao cũng vậy. Ý tao là, nếu tao có gì muốn nói, tao có thể nói thẳng với mày mà, phải không? Nhưng thấy mọi người đều viết thư nên tao nhờ Sanhua ghi lại những gì tao nói.
 Nghĩ lại thì, chúng ta đã trải qua bao nhiêu chuyện rồi nhỉ? Từ Huanglong đến Bãi Đen, rồi đến Rinascita. Từ bánh bao rồng đến bát canh san hô, rồi Pizza Tropicale. Dù chuyến đi có lúc khó khăn, nhưng cuối cùng chẳng gì có thể cản được chúng ta.
-&lt;s&gt;Ừm... hừm, ta muốn gì nhỉ...? Khoan, đừng viết cái đó!&lt;/s&gt;
-Ta mong từ hôm nay trở đi, chúng ta sẽ luôn no đủ và vui vẻ. À, nếu ngươi gặp rắc rối, đừng quên gọi ta nhé. Việc của ngươi cũng là việc của ta mà.
+&lt;s&gt;Ừm... hừm, tao muốn gì nhỉ...? Khoan, đừng viết cái đó!&lt;/s&gt;
+Tao mong từ hôm nay trở đi, chúng ta sẽ luôn no đủ và vui vẻ. À, nếu mày gặp rắc rối, đừng quên gọi tao nhé. Việc của mày cũng là việc của tao mà.
 Abby"</t>
         </is>
       </c>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Đây không đơn thuần là một bức tranh cắt dán từ những chất liệu rời rạc, mà là sự diễn giải về nguồn cảm hứng và tư tưởng của chủ nghĩa kiến tạo. Người sáng tạo ra nó khởi đầu sự nghiệp bằng những đột phá táo bạo, nhưng lại không được đánh giá đúng mức. Thế nhưng, Carlotta đã nhìn ra "viên ngọc ẩn" ấy, miêu tả tác phẩm của cô là "ấn tượng của sự khác biệt với Dodget thơ mộng ám ảnh." Giờ đây, khi đã là một nghệ sĩ sắp đặt nổi tiếng ở Ragunna, cô đã tạo nên tác phẩm tinh xảo này như một món quà tri ân đặc biệt dành cho Carlotta – người đã luôn bảo trợ và tin tưởng cô.</t>
+          <t>Đây không đơn thuần là một bức tranh cắt dán từ những chất liệu rời rạc, mà là sự diễn giải về nguồn cảm hứng và tư tưởng của chủ nghĩa kiến tạo. Người sáng tạo ra nó khởi đầu sự nghiệp bằng những đột phá táo bạo, nhưng lại không được đánh giá đúng mức. Thế nhưng, Carlotta đã nhìn ra "viên ngọc ẩn" ấy, miêu tả tác phẩm của cô là "ấn tượng của sự khác biệt với nét thơ mộng ám ảnh." Giờ đây, khi đã là một nghệ sĩ sắp đặt nổi tiếng ở Ragunna, cô đã tạo nên tác phẩm tinh xảo này như một món quà tri ân đặc biệt dành cho Carlotta – người đã luôn bảo trợ và tin tưởng cô.</t>
         </is>
       </c>
     </row>
@@ -8857,13 +8857,13 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Battier, tay câu cá cừ khôi nhất của &lt;te href=850108&gt;Gánh Hề&lt;/te&gt;, một ngày nọ đã gặp rắc rối trong chuyến câu cá vốn dĩ bình thường. Chỉ với cây lao quen thuộc, hắn chiến đấu chống lại một &lt;te href=850081&gt;Discord&lt;/te&gt; dưới nước hung dữ đến mức sớm kéo hắn xuống lòng biển sâu. May mắn thay, Roccia đã cảm nhận được điều bất thường khi Battier không trở về như dự định và nhanh chóng tập hợp các thành viên trong gánh để lập một đội cứu hộ nhỏ. Họ lùng sục vùng biển gần đó và cuối cùng đã kéo được Battier ướt sũng, mệt mỏi lên bờ. Thế nhưng, cây lao cũ kỹ của hắn lại không được may mắn như vậy—nó bị mắc kẹt trong thân &lt;te href=850081&gt;Discord&lt;/te&gt;, và cả hai đều bị cuốn vào xoáy nước dưới biển.
+          <t>Battier, tay câu cá cừ khôi nhất của &lt;te href=850108&gt;Gánh Hề&lt;/te&gt;, một ngày nọ đã gặp rắc rối trong chuyến câu cá vốn dĩ bình thường. Chỉ với cây lao quen thuộc, hắn chiến đấu chống lại một &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; dưới nước hung dữ đến mức sớm kéo hắn xuống lòng biển sâu. May mắn thay, Roccia đã cảm nhận được điều bất thường khi Battier không trở về như dự định và nhanh chóng tập hợp các thành viên trong gánh để lập một đội cứu hộ nhỏ. Họ lùng sục vùng biển gần đó và cuối cùng đã kéo được Battier ướt sũng, mệt mỏi lên bờ. Thế nhưng, cây lao cũ kỹ của hắn lại không được may mắn như vậy—nó bị mắc kẹt trong thân &lt;te href=850081&gt;Tacet Discord&lt;/te&gt;, và cả hai đều bị cuốn vào xoáy nước dưới biển.
 Mất cây lao, Battier cảm thấy như mất đi một phần linh hồn. Hắn dành hàng giờ gài bẫy mà chẳng bắt được gì, như thể đàn cá cũng cảm nhận được sự thiếu vắng ấy. Có ngày, hắn chỉ nằm dài trên cát đen của Bãi Biển, ngước nhìn bầu trời mờ ảo. Ngay cả những đám mây cũng như trêu chọc hắn, biến hình thành đàn cá lững lờ trôi xa mãi.
 "Aaaah—!" hắn gào lên với bầu trời trong tuyệt vọng.
 Như để xoa dịu tâm hồn hắn, những đám mây bắt đầu tách ra từng lớp, những tia sáng lấp lánh chiếu xuống, biến bầu trời thành một biển sáng lung linh. Ngay chính giữa, cây lao đã mất của hắn xuất hiện, từ từ hạ xuống như một món quà thần thánh từ thiên đường, lấp lánh dưới ánh nắng vàng rực. Nó rơi thẳng vào tay hắn như chưa từng rời đi. Đồng thời, đàn cá lại ùa đến quanh hắn, nhảy múa trên không và dưới nước.
 Được khích lệ bởi điều kỳ diệu này, Battier kéo lên một mẻ cá đầy ắp mang về cho gánh. Roccia và &lt;te href=850122&gt;Pero&lt;/te&gt; dùng số cá ấy chế biến một bữa tiệc thịnh soạn—mực nướng, súp nghêu sữa, cá phi lê ướp tiêu, và đủ thứ khác. Không khí tràn ngập hương thơm hải sản khi mọi người quây quần bên đống lửa, cười đùa và ăn uống cùng nhau. Có người còn cầm xiên cá làm kiếm, diễn một màn hài kịch khiến cả đám cười bò. Nhìn đám đông vui vẻ ấy, Battier cảm thấy lòng mình ấm áp—đó là niềm vui giản đơn khi được cần đến và niềm hứng khởi khi câu cá cho những người thật sự trân trọng hắn.
 Trong khi mọi người đang thưởng thức bữa tiệc, Roccia trao đổi một cái nhìn nhanh với Pero trước khi giấu chiếc Cloudcaster họ đã dùng trước đó vào đống cỏ khô. Là một người quản lý đạo cụ, cô hiểu rõ ý nghĩa của những vật phẩm đối với mỗi người. Dù khó khăn đến đâu, cô luôn tìm cách lấy lại những gì đã mất—dù là từ biển cả hay từ bầu trời. Sau khi đánh bóng chúng cẩn thận, cô sẽ lên kế hoạch cho một cuộc hội ngộ đầy xúc động và kịch tính, như cách cô đã làm với cây lao vàng của Battier.
-Từ ngày đó, gánh hát có thêm một vở diễn mới: Battier và Cây Golden Harpoon. Đoàn diễn lại câu chuyện kỳ diệu này với những con cá nướng trên tay và trái tim tràn ngập tiếng cười.</t>
+Từ ngày đó, gánh hát có thêm một vở diễn mới: Battier và Cây Lao Vàng. Đoàn diễn lại câu chuyện kỳ diệu này với những con cá nướng trên tay và trái tim tràn ngập tiếng cười.</t>
         </is>
       </c>
     </row>
@@ -8940,7 +8940,7 @@
 Nhưng khi họ tiến sâu vào trung tâm bão, những đôi mắt phát sáng lờ mờ bắt đầu nổi lên trong làn nước tối, và những lời thì thầm đáng sợ vang lên theo gió. Sự điềm tĩnh của Roccia dường như lung lay—bàn tay cô run rẩy khi cất kịch bản đi và bám chặt vào mép cabin. Cuối cùng, ngay cả Tina cứng rắn cũng nhận ra Roccia đang run. Không biết an ủi thế nào, Tina thay vào đó cất giọng hát, giọng cô mạnh mẽ và vững vàng, cộng hưởng với con tàu &lt;te href=850082&gt;Echo&lt;/te&gt;. Trong tình huống này, tất cả những gì cô có thể làm là giữ vững con tàu qua những làn sóng dữ dội, điều đó đòi hỏi sự tập trung tuyệt đối.
 Rồi, một giọng hát nhẹ nhàng hơn hòa vào. Tina quay lại và thấy Roccia đang co ro gần cabin, hát theo với giọng run run. Dù đôi mắt cô vẫn lấp lánh nỗi sợ, Roccia không quên nhiệm vụ của mình. Cô lấy kính viễn vọng ra, quan sát đường chân trời tối đen để xác định lộ trình. Giọng Tina càng lúc càng mạnh mẽ, hòa quyện với những nốt nhạc nhẹ nhàng của Roccia, át đi những lời thì thầm đáng sợ xung quanh. Bắt được dòng chảy phù hợp, con tàu lao về phía trước, xuyên qua cơn bão và đón ánh bình minh đầu tiên.
 Trở lại bờ, Roccia lại bình tĩnh và điềm đạm như chưa từng có chuyện gì. Từ ngày đó, Thuyền phó Roccia đã dẫn dắt mọi chuyến hải trình với đôi tay vững vàng, luôn đưa mọi người về nhà an toàn.
-"Roccia?" Tina, người nổi tiếng với sự thẳng thắn, được hỏi sau đó. Cô cười, ánh mắt lấp lánh niềm tự hào. "Cô ấy cứng cỏi và đáng tin cậy—một cô gái tốt, xứng đáng được yêu thương và chăm sóc. Còn về cao độ của cô ấy... thì, có thể chưa hoàn hảo, nhưng trái tim thì luôn có."</t>
+"Roccia à?" Tina, người nổi tiếng với sự thẳng thắn, được hỏi sau đó. Cô cười, ánh mắt lấp lánh niềm tự hào. "Cô ấy cứng cỏi và đáng tin cậy—một cô gái tốt, xứng đáng được yêu thương và chăm sóc. Còn về cao độ của cô ấy... thì, có thể chưa hoàn hảo, nhưng trái tim thì luôn có."</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9017,7 @@
 Luca vẫn nhớ ngày Roccia đưa tấm vé ấy cho mình sau khi được cứu khỏi Strand. Roccia lúc đó điềm tĩnh và vững vàng, dù chắc chẳng lớn hơn Luca là bao. Cô ấy làm được đủ thứ—giúp đỡ những người hành hương lạc bước dạt vào bờ, nấu ăn cho cả đoàn, ghi lại những khoảnh khắc vui vẻ, sưu tầm vỏ sò và Luceanite, thậm chí còn nạp đạn cho súng bắn hoa giấy. Và tất nhiên, động viên những đứa trẻ mới đến như Luca khi chúng nhớ nhà cũng là một phần công việc của cô.
 Một hôm, Luca ngước lên nhìn Roccia, mũi sniffling, tay nắm chặt tấm vé. "Con nhớ mẹ, Roccia… Con muốn về nhà gặp mẹ. Nhưng con chỉ có vé một chiều, mà lại làm mất rồi…"
 Tấm vé trong tay ghi dòng chữ "Vé Một Chiều Đến Xứ Sở Thần Tiên", viết tay rất đẹp với những bông hoa nhỏ xinh xung quanh.
-Roccia lập tức hiểu chuyện gì đang xảy ra. Hội Ánh Sáng, lúc nào cũng bận trục xuất những ai dám thách thức họ, chắc chắn sẽ không tử tế đến mức làm ra một tấm vé ấm áp như thế. Chắc chắn mẹ của Luca đã tự tay làm nó, mong mang lại chút an ủi cho con gái. Roccia muốn nói thật với Luca. "Hội Ánh Sáng không làm những tấm vé này đâu, Luca. Nhìn Dodget chữ, có vẻ một người phụ nữ tốt bụng đã làm nó… một người yêu thương con." "Đó là mẹ con, Luca. Những tấm vé này không thể đưa con về nhà được, nên có mất cũng chẳng sao."
+Roccia lập tức hiểu chuyện gì đang xảy ra. Hội Ánh Sáng, lúc nào cũng bận trục xuất những ai dám thách thức họ, chắc chắn sẽ không tử tế đến mức làm ra một tấm vé ấm áp như thế. Chắc chắn mẹ của Luca đã tự tay làm nó, mong mang lại chút an ủi cho con gái. Roccia muốn nói thật với Luca. "Hội Ánh Sáng không làm những tấm vé này đâu, Luca. Nhìn nét chữ, có vẻ một người phụ nữ tốt bụng đã làm nó… một người yêu thương con." "Đó là mẹ con, Luca. Những tấm vé này không thể đưa con về nhà được, nên có mất cũng chẳng sao."
 Nhưng cô biết nói thế chỉ khiến Luca khóc nhiều hơn thôi.
 Roccia suy nghĩ một chút, rồi rời đi và trở lại với một tấm vé mới—một "Vé Khứ Hồi", được trang trí bằng những bông hoa vẽ tay, vỏ sò, và một con dấu vẽ tay ghi "Đã Đến Xứ Sở Thần Tiên".
 Luca nở nụ cười tươi rói khi nhận lấy, ôm chặt nó trong tay.
@@ -9173,9 +9173,9 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Những người đến rồi đi trong &lt;te href=850108&gt;Đoàn Kẻ Ngốc&lt;/te&gt;, mỗi người đều truyền cảm hứng cho những màn trình diễn sôi động của Roccia. Những vở diễn như "Battier và Cây Golden Harpoon", "Tina – Hoa Tiêu Soprano", "Brant – Thuyền Trưởng Nổi Loạn", và "&lt;te href=850122&gt;Pero&lt;/te&gt; – Peculiar Box" đã trở thành huyền thoại. Đến nay, cô và đoàn đã biểu diễn hơn hai trăm buổi, thắp sáng từng ngóc ngách của Penitent's End.
+          <t>Những người đến rồi đi trong &lt;te href=850108&gt;Đoàn Kẻ Ngốc&lt;/te&gt;, mỗi người đều truyền cảm hứng cho những màn trình diễn sôi động của Roccia. Những vở diễn như "Battier và Cây Lao Vàng", "Tina – Hoa Tiêu Soprano", "Brant – Thuyền Trưởng Nổi Loạn", và "&lt;te href=850122&gt;Pero&lt;/te&gt; – Chiếc Hộp Kỳ Lạ" đã trở thành huyền thoại. Đến nay, cô và đoàn đã biểu diễn hơn hai trăm buổi, thắp sáng từng ngóc ngách của Penitent's End.
 Đoàn không có nhiều thứ, nên với vai trò quản lý đạo cụ, Roccia trở thành bậc thầy biến những vật dụng thường ngày thành phép màu sân khấu. Chiếc lao vàng của Battier từng đóng vai vương trượng của Primus, kiếm của hiệp sĩ lang thang, thậm chí là dao găm của La Guardia. Con tàu &lt;te href=850082&gt;Echo&lt;/te&gt; từng hóa thân thành thuyền cứu sinh, ủng khổng lồ của gã khổng lồ cối xay gió, thậm chí là con mắt của quái vật biển.
-Nhiều năm trời, Roccia và Pero khám phá từng ngóc ngách của căn cứ đoàn, từng bờ biển của hòn đảo. Họ nhặt vô số Luceanites từ Bãi Strand và ngắm nghìn bình minh. Like những người khác, họ đã bị giam cầm ở nơi này quá lâu. Đoàn kịch là mái ấm ấm áp cho mọi thành viên, nhưng không tránh khỏi, có người vẫn mơ về chân trời xa, kẻ lại nhớ về quê nhà đã bỏ lại.
+Nhiều năm trời, Roccia và Pero khám phá từng ngóc ngách của căn cứ đoàn, từng bờ biển của hòn đảo. Họ nhặt vô số Luceanites từ Bãi Strand và ngắm nghìn bình minh. Giống như những người khác, họ đã bị giam cầm ở nơi này quá lâu. Đoàn kịch là mái ấm ấm áp cho mọi thành viên, nhưng không tránh khỏi, có người vẫn mơ về chân trời xa, kẻ lại nhớ về quê nhà đã bỏ lại.
 Khi tiếng nhạc &lt;te href=850102&gt;Carnevale&lt;/te&gt; mong đợi từ lâu trôi dạt qua biển từ &lt;te href=850097&gt;Ragunna&lt;/te&gt;, cùng những cánh hoa chúc mừng &lt;te href=850103&gt;Laureate&lt;/te&gt; đăng quang, Đoàn Kẻ Ngốc cảm nhận được sức hút không thể cưỡng lại của cơn gió trở về.
 Ký ức tuổi thơ của Roccia mờ nhạt, nhưng khi theo chân Brant và đoàn bước vào những con phố Ragunna, mùi bánh pizza mới ra lò từ tiệm Trattoria Margherita và những khúc ca vang lên từ Nhà hát Opera Odyssey đã khuấy động điều gì đó sâu thẳm trong lòng cô, như với tất cả mọi người.
 Dưới bầu trời trong xanh và ánh mặt trời vàng óng, những con phố thành phố trải dài như một sân khấu chờ đợi cô. Một làn gió nhẹ như mở hé chiếc hộp cô luôn giấu mình bên trong, mời gọi cô bước vào thế giới rộng lớn hơn. Với vòng tay rộng mở và trái tim vững vàng, Roccia đặt những bước chân đầu tiên vào Ragunna, chào đón một ngày mai tươi sáng hơn.
@@ -11071,9 +11071,9 @@
       <c r="M158" t="inlineStr">
         <is>
           <t>Jinzhou, thành trì trấn giữ biên giới Huanglong, đồng thời là cửa ngõ đầu tiên của vùng đất này đối với những ai đến từ hải ngoại. Dãy Núi Linh Hồn trải dài từ bắc xuống nam, chia Huanglong thành hai miền: Nội Huanglong với sáu thành phố, và Ngoại Huanglong, nơi Jinzhou kiên cường đứng vững. Những ngọn núi này tạo thành bức tường thiên nhiên, với những hẻm núi là lối vào duy nhất dẫn vào Nội Huanglong, được canh giữ ngày đêm bởi đội Midnight Rangers của Jinzhou.
-Việc xây dựng pháo đài đầu tiên ở Ngoại Huanglong bắt đầu từ khi Tacet Field Norfall Barrens xuất hiện, nơi các đợt bùng phát Tacet Discord bắt đầu tàn phá khu vực. Sau nhiều tháng chiến đấu khốc liệt, quân đội không còn chịu nổi sức tấn công của các đợt bùng phát và buộc phải rút lui về Gorges of Spirits để tử thủ. Những chiến binh đã kiên cường chiến đấu suốt nhiều ngày, khi phòng tuyến liên tục bị phá vỡ rồi giành lại. Trong thời gian đó, Hiện tượng Waveworn trên khắp Huanglong dường như đang trong giai đoạn hoạt động mạnh, và có vẻ như các Tacet Discord được dẫn dắt bởi một thủ lĩnh bí ẩn, nhằm hội tụ về Nội Huanglong.
-Vào thời khắc quyết định, quân tiếp viện từ sáu thành phố đã được điều đến Gorges of Spirits, nơi các chiến binh biên giới vẫn chiến đấu với ý chí bất khuất. Khi trận chiến lên đến đỉnh điểm, sự xuất hiện của kẻ Vô Vương đã phá vỡ thế bế tắc. Bất cứ nơi nào hắn xuất hiện, bóng tối bao trùm bầu trời, và một bầu không khí ngột ngạt bao trùm, khiến các chiến binh nghẹt thở. Dù vậy, họ vẫn kiên cường giữ vững phòng tuyến, sẵn sàng hy sinh để爭取 thời gian phá hủy lối vào Gorges of Spirits, ngăn chặn đợt bùng phát Tacet Discord. Họ làm điều đó với ý thức rằng phần lớn trong số họ sẽ bị mắc kẹt ở Ngoại Huanglong cùng với lũ Tacet Discord mãi mãi.
-Trong khoảnh khắc sinh tử đó, tiếng gầm vang dội của một con Loong hùng mạnh vang lên từ sâu thẳm Gorges of Spirits, như sấm truyền khắp đại địa. Tiếng gầm ấy vang dội từ hẻm núi, đẩy lùi đội quân Tacet Discord đang chuẩn bị tràn vào. Trong nháy mắt, một con Loong bay vút trên bầu trời, xua tan mây đen và mang ánh sáng trở lại. Rồi một nhân vật kỳ lạ với đôi mắt vàng xuất hiện, đứng giữa lũ Tacet Discord và các chiến binh, đối đầu với kẻ Vô Vương trong một cuộc giằng co quyết liệt. Như trong thơ có câu: "Giáp phục lấp lánh vảy Loong vàng dưới ánh dương." Khi quân tiếp viện từ sáu thành phố đến, liên quân đã đẩy lùi đợt bùng phát Tacet Discord và kẻ Vô Vương về phía bắc Trung Nguyên.
+Việc xây dựng pháo đài đầu tiên ở Ngoại Huanglong bắt đầu từ khi Tổ Tacet Norfall Barrens xuất hiện, nơi các đợt bùng phát Tacet Discord bắt đầu tàn phá khu vực. Sau nhiều tháng chiến đấu khốc liệt, quân đội không còn chịu nổi sức tấn công của các đợt bùng phát và buộc phải rút lui về Hẻm Núi Linh Hồn để tử thủ. Những chiến binh đã kiên cường chiến đấu suốt nhiều ngày, khi phòng tuyến liên tục bị phá vỡ rồi giành lại. Trong thời gian đó, Hiện tượng Waveworn trên khắp Huanglong dường như đang trong giai đoạn hoạt động mạnh, và có vẻ như các Tacet Discord được dẫn dắt bởi một thủ lĩnh bí ẩn, nhằm hội tụ về Nội Huanglong.
+Vào thời khắc quyết định, quân tiếp viện từ sáu thành phố đã được điều đến Hẻm Núi Linh Hồn, nơi các chiến binh biên giới vẫn chiến đấu với ý chí bất khuất. Khi trận chiến lên đến đỉnh điểm, sự xuất hiện của kẻ Vô Vương đã phá vỡ thế bế tắc. Bất cứ nơi nào hắn xuất hiện, bóng tối bao trùm bầu trời, và một bầu không khí ngột ngạt bao trùm, khiến các chiến binh nghẹt thở. Dù vậy, họ vẫn kiên cường giữ vững phòng tuyến, sẵn sàng hy sinh để爭取 thời gian phá hủy lối vào Hẻm Núi Linh Hồn, ngăn chặn đợt bùng phát Tacet Discord. Họ làm điều đó với ý thức rằng phần lớn trong số họ sẽ bị mắc kẹt ở Ngoại Huanglong cùng với lũ Tacet Discord mãi mãi.
+Trong khoảnh khắc sinh tử đó, tiếng gầm vang dội của một con Loong hùng mạnh vang lên từ sâu thẳm Hẻm Núi Linh Hồn, như sấm truyền khắp đại địa. Tiếng gầm ấy vang dội từ hẻm núi, đẩy lùi đội quân Tacet Discord đang chuẩn bị tràn vào. Trong nháy mắt, một con Loong bay vút trên bầu trời, xua tan mây đen và mang ánh sáng trở lại. Rồi một nhân vật kỳ lạ với đôi mắt vàng xuất hiện, đứng giữa lũ Tacet Discord và các chiến binh, đối đầu với kẻ Vô Vương trong một cuộc giằng co quyết liệt. Như trong thơ có câu: "Giáp phục lấp lánh vảy Loong vàng dưới ánh dương." Khi quân tiếp viện từ sáu thành phố đến, liên quân đã đẩy lùi đợt bùng phát Tacet Discord và kẻ Vô Vương về phía bắc Trung Nguyên.
 Sau trận chiến này, Ngoại Huanglong đã hồi sinh từ đống tro tàn. Sự xuất hiện của cả Threnodian lẫn sinh vật thần thánh báo hiệu nhu cầu xây dựng một thành phố mới để trở thành pháo đài biên giới của Huanglong. Lấy cảm hứng từ âm "Jin" trong "Guan Jin" (nghĩa là "ải quan"), và hình dáng của chữ "Jin" tượng trưng cho tiếng gầm của Loong, thành phố này được đặt tên là Jinzhou.</t>
         </is>
       </c>
@@ -11146,7 +11146,7 @@
           <t>Một báo cáo từ Bộ Phát triển, được lưu trữ tại Tòa Thị chính. Ngày nộp báo cáo cho thấy nó đã được đệ trình từ hàng thập kỷ trước.
 Phòng Cơ sở hạ tầng thuộc Bộ Phát triển tại Jinzhou, Huanglong:
 Giai đoạn II của Dự án Mở rộng Jinzhou đã hoàn thành công tác chuẩn bị ban đầu. Chúng tôi hiện đang nộp đơn xin phê duyệt sử dụng đất để tiến hành xây dựng. Dưới đây là các thông tin liên quan đến dự án:
-I. Overview về đơn vị thi công:
+I. Tổng quan về đơn vị thi công:
 Đội Phát triển Đất đai thuộc Phòng Cơ sở hạ tầng là đơn vị thi công dự án xây dựng trực thuộc Bộ Phát triển Jinzhou, chịu trách nhiệm quản lý các hoạt động xây dựng trong khu vực Jinzhou. Ban đầu, đội gồm 60 nhân viên. Sau quá trình tuyển dụng và điều chuyển trong giai đoạn hậu chiến, đội đã tăng lên 400 thành viên tạm thời. Trong đó có 31 người từ đội ngũ ban đầu, 190 người được điều chuyển từ Học viện Hoa Hư, Đội Kỵ binh Bóng đêm và Phòng Quốc phòng thuộc Bộ Phát triển, 120 tình nguyện viên từ Jinzhou, 50 người được điều chuyển từ các khu vực khác, và 9 người có nguồn gốc không rõ.</t>
         </is>
       </c>
@@ -11219,13 +11219,13 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Cẩm nang du lịch do Pioneer Association biên soạn, giới thiệu về vùng đồng bằng trung tâm Jinzhou.
-[Chào đón năm mới bằng luyện tập mùa đông] Liondance Troupe
-Mỗi mùa đông, Liondance Troupe tạm ngừng hoạt động khi các thành viên lên đường đến đồng bằng trung tâm để tập luyện khép kín tại khu huấn luyện ở Taoyuan Vale.
+          <t>Cẩm nang du lịch do Hiệp Hội Tiên Phong biên soạn, giới thiệu về vùng đồng bằng trung tâm Jinzhou.
+[Chào đón năm mới bằng luyện tập mùa đông] Đoàn Múa Lân
+Mỗi mùa đông, Đoàn Múa Lân tạm ngừng hoạt động khi các thành viên lên đường đến đồng bằng trung tâm để tập luyện khép kín tại khu huấn luyện ở Thung Lũng Đào Nguyên.
 Trái với suy nghĩ của nhiều người, thời gian nghỉ của đoàn không hề là khoảng thời gian nghỉ ngơi. Trong thời gian này, các thành viên tập trung cao độ để trau chuốt nhân vật, mài giũa kỹ năng, chế tác đạo cụ, diễn tập tiết mục sắp tới và tích lũy năng lượng cho màn trình diễn tại lễ diễu hành năm mới Suan'ni, khi chú sư tử thực sự "thức tỉnh".
-Trong mùa nghỉ, nếu các thành viên Liondance Troupe tình cờ đi qua Jinzhou, họ thường bị trêu chọc bằng những câu như: "Này, Lingyang, năm nay chú sư tử của cậu 'thức dậy' khi nào thế?" hay "Ông Wufang, đến lúc 'đánh thức' sư tử rồi đấy!"
-[Khu huấn luyện Liondance Troupe] Bài tập của vũ công múa lân
-Đây là Cọc Hoa Mai, được xếp theo hình zigzag với mật độ giảm dần, tạo thành một thử thách khó nhằn cho hai đầu sư tử tranh nhau chỗ đứng và với tới quả ớt đỏ treo trên cọc cao nhất. Do không gian ở Jinzhou hạn chế, Liondance Troupe đã dựng bài tập này trong sân tại Taoyuan Vale.
+Trong mùa nghỉ, nếu các thành viên Đoàn Múa Lân tình cờ đi qua Jinzhou, họ thường bị trêu chọc bằng những câu như: "Này, Lingyang, năm nay chú sư tử của cậu 'thức dậy' khi nào thế?" hay "Ông Wufang, đến lúc 'đánh thức' sư tử rồi đấy!"
+[Khu huấn luyện Đoàn Múa Lân] Bài tập của vũ công múa lân
+Đây là Cọc Hoa Mai, được xếp theo hình zigzag với mật độ giảm dần, tạo thành một thử thách khó nhằn cho hai đầu sư tử tranh nhau chỗ đứng và với tới quả ớt đỏ treo trên cọc cao nhất. Do không gian ở Jinzhou hạn chế, Đoàn Múa Lân đã dựng bài tập này trong sân tại Thung Lũng Đào Nguyên.
 Giữa làn cánh đào lả tả, những vũ công múa lân trẻ bước đi uyển chuyển trên các cọc gỗ, tạo nên một khung cảnh độc đáo chỉ có ở đồng bằng trung tâm.</t>
         </is>
       </c>
@@ -11295,10 +11295,10 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>["Lion Dance Ngũ Phương: Sự Kết Hợp Giữa Âm Nhạc và Chuyển Động" Dance Huanglong Thái Bình
-Dance Huanglong Thái Bình, hay còn gọi là múa sư tử ở Jinzhou, khởi nguồn là một điệu múa trận nhằm tưởng nhớ những chiến thắng của quân đội Huanglong. Trung tâm của màn trình diễn là hình ảnh con sư tử, biểu tượng cho sự trở về trong vinh quang, hòa cùng nhịp trống dồn dập, âm nhạc sôi động và những chuyển động mạnh mẽ. Những yếu tố này không chỉ tiếp thêm sinh lực cho các vũ công mà còn khơi dậy tinh thần khán giả.
+          <t>["Múa Sư Tử Ngũ Phương: Sự Kết Hợp Giữa Âm Nhạc và Chuyển Động" Vũ Điệu Huanglong Thái Bình
+Vũ Điệu Huanglong Thái Bình, hay còn gọi là múa sư tử ở Jinzhou, khởi nguồn là một điệu múa trận nhằm tưởng nhớ những chiến thắng của quân đội Huanglong. Trung tâm của màn trình diễn là hình ảnh con sư tử, biểu tượng cho sự trở về trong vinh quang, hòa cùng nhịp trống dồn dập, âm nhạc sôi động và những chuyển động mạnh mẽ. Những yếu tố này không chỉ tiếp thêm sinh lực cho các vũ công mà còn khơi dậy tinh thần khán giả.
 Từ một điệu múa trận, múa sư tử dần trở thành biểu tượng của lòng dũng cảm và nghi lễ cầu bình an—xua đuổi điềm xấu, nghênh đón vận may.
-Như câu nói rằng, Lion Dance Ngũ Phương minh họa sự thuần phục và tinh nghịch của sư tử trong Thất Tinh. Muốn theo Ngũ Phương, phải hiểu Thất Tinh, và ngược lại.
+Như câu nói rằng, Múa Sư Tử Ngũ Phương minh họa sự thuần phục và tinh nghịch của sư tử trong Thất Tinh. Muốn theo Ngũ Phương, phải hiểu Thất Tinh, và ngược lại.
 Những vũ công múa sư tử tràn đầy năng lượng, thay đổi bước chân để thể hiện đủ cung bậc cảm xúc từ vui tươi đến buồn bã, từ giận dữ đến say xỉn. Nhịp trống cũng biến đổi theo, lúc dịu dàng, lúc như sấm dội. Các vũ công hòa theo nhịp điệu để khắc họa tâm trạng và động tác của sư tử—lúc giật mình, lúc vui mừng, lúc chạy nhảy, lúc dừng lại. Khi sư tử bất ngờ, trống ngừng hẳn; khi nó nhìn quanh, nhịp trống nhẹ nhàng như mưa phùn. Khi sư tử hăng hái, trống dồn dập; và khi nó gầm lên, nhịp trống như sấm vang.
 ]</t>
         </is>
@@ -11455,11 +11455,11 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Chuyện Lạ ở Huanglong: Calamity Ba Đầu&lt;/i&gt;
+          <t>&lt;i&gt;Chuyện Lạ ở Huanglong: Tai Họa Ba Đầu&lt;/i&gt;
 Desorock Highland, từng là thung lũng sông màu mỡ, là nguồn của vô số dòng suối nuôi dưỡng vùng hạ lưu.
-Sau khi Hiện tượng Waveworn xuất hiện, thời tiết bất thường đã rút cạn hầu hết các nguồn nước, biến khu vực hồ thành vùng đất khô cằn và sinh ra các Tacet Field cùng Tacet Discord.
+Sau khi Hiện tượng Waveworn xuất hiện, thời tiết bất thường đã rút cạn hầu hết các nguồn nước, biến khu vực hồ thành vùng đất khô cằn và sinh ra các Tổ Tacet cùng Tacet Discord.
 Không ai biết con chim đó xuất hiện từ khi nào, nhưng như một con kền kền săn mồi thối, nó lởn vởn trên vùng đất này như điềm báo tai ương, xuất hiện bất cứ nơi nào có cái chết.
-Là tiền tuyến chống lại sự bùng phát của Tacet Discord, Desorock Highland đã trở thành nghĩa địa của vô số chiến binh. Bird Calamity lưu lại quá lâu đến nỗi nó còn làm tổ trên Vách Olecranon bên hồ, chờ đợi cái chết đến với những kẻ gần đó.
+Là tiền tuyến chống lại sự bùng phát của Tacet Discord, Desorock Highland đã trở thành nghĩa địa của vô số chiến binh. Chim Tai Họa lưu lại quá lâu đến nỗi nó còn làm tổ trên Vách Olecranon bên hồ, chờ đợi cái chết đến với những kẻ gần đó.
 Một số người tin rằng sự ra đi của nó khỏi Cao nguyên báo hiệu chấm dứt những trận chiến bất tận ở Jinzhou, nhưng nỗi sợ vẫn còn, vì không ai biết tổ tiếp theo của nó sẽ xuất hiện ở đâu.</t>
         </is>
       </c>
@@ -11892,9 +11892,9 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Sống sót nơi hoang dã là một thử thách khắc nghiệt và không khoan nhượng, nên đừng mong đợi một kẻ Lưu Đày sẽ tuân theo những quy tắc văn minh. Hầu hết bọn họ sống theo luật rừng, nơi sức mạnh và mưu mẹo là tài sản đáng tin cậy duy nhất. Chúng rèn luyện thể xác và mài giũa kỹ năng vũ khí trong các trại huấn luyện, học cách nhận diện thực vật và khoáng sản quý hiếm, di chuyển qua những con đường bí mật trên núi và sông ngòi mà chỉ chúng biết. Một số thậm chí còn phát triển kỹ thuật Dodge sự chú ý của Echo.
+          <t>Sống sót nơi hoang dã là một thử thách khắc nghiệt và không khoan nhượng, nên đừng mong đợi một kẻ Lưu Đày sẽ tuân theo những quy tắc văn minh. Hầu hết bọn họ sống theo luật rừng, nơi sức mạnh và mưu mẹo là tài sản đáng tin cậy duy nhất. Chúng rèn luyện thể xác và mài giũa kỹ năng vũ khí trong các trại huấn luyện, học cách nhận diện thực vật và khoáng sản quý hiếm, di chuyển qua những con đường bí mật trên núi và sông ngòi mà chỉ chúng biết. Một số thậm chí còn phát triển kỹ thuật né tránh sự chú ý của Tổ Tacet.
 Những kỹ năng sinh tồn này được các phe phái Lưu Đày coi như báu vật, quý giá như mạng sống. Nhưng khi giá cả hợp lý, chúng cũng không ngại cung cấp dịch vụ cho dân thường, lữ khách hay thương nhân—làm sát thủ, tìm kiếm nguyên liệu quý, hoặc xử lý những công việc không mấy danh giá. Dù giao dịch với kẻ Lưu Đày không bị cấm ở Jinzhou, nhưng cũng không được pháp luật bảo vệ. Nếu một kẻ Lưu Đày coi cậu là miếng mồi dễ dàng, chúng có thể đơn giản bỏ qua mọi thỏa thuận, cướp sạch và bỏ mặc cậu bên vệ đường.
-Chỉ một số ít Lưu Đày còn giữ được chút phẩm giá hay danh dự. Dù chúng từ chối chính quyền, nhưng vẫn coi mình là một phần của xã hội loài người. Những kẻ này sẽ chiến đấu chống lại Echo khi có thể, bảo vệ khu định cư của mình, và đôi khi còn lập những thỏa thuận ngầm không xâm phạm lẫn nhau với các phe phái Lưu Đày khác.</t>
+Chỉ một số ít Lưu Đày còn giữ được chút phẩm giá hay danh dự. Dù chúng từ chối chính quyền, nhưng vẫn coi mình là một phần của xã hội loài người. Những kẻ này sẽ chiến đấu chống lại Tổ Tacet khi có thể, bảo vệ khu định cư của mình, và đôi khi còn lập những thỏa thuận ngầm không xâm phạm lẫn nhau với các phe phái Lưu Đày khác.</t>
         </is>
       </c>
     </row>
@@ -11964,11 +11964,11 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Đây là... bản ghi chép đánh giá phim từ Liên hoan Film Solaris ở Somnoire à?
+          <t>Đây là... bản ghi chép đánh giá phim từ Liên hoan Phim Solaris ở Somnoire à?
 Ôi trời, người ta còn tổ chức liên hoan phim ở Somnoire cơ à?
-Rating bởi [Giấc Mơ Thuần Khiết] Dorothy Kẻ Phiêu Lưu Kỳ Diệu; Điểm: 9/10
+Đánh giá bởi [Giấc Mơ Thuần Khiết] Dorothy Kẻ Phiêu Lưu Kỳ Diệu; Điểm: 9/10
 Ôi, quá đáng! Nhà biên kịch này... thật quá quắt! Tôi không chấp nhận cái kết này! Tại sao, tại sao, tại sao?! Jiu đã hứa sẽ cho Yuehui một cái kết hạnh phúc, vậy mà lại nói: "Tôi không muốn nói lời tạm biệt, cũng không muốn hứa hẹn gì với em." Nghĩa là sao chứ?! Cảnh cuối, khi họ đoàn tụ trên lưng những con chim lớn, đẹp đấy... nhưng tại sao họ không thể quay lại như xưa? Khôngoo! Thật tệ! Tôi trừ một điểm vì cái kết này!
-Rating bởi [Ước Nguyện Dưới Bầu Trời Trong Xanh] Cô Cam; Điểm: 8/10
+Đánh giá bởi [Ước Nguyện Dưới Bầu Trời Trong Xanh] Cô Cam; Điểm: 8/10
 Đây là một bộ phim về tình yêu, và cảnh khiến tôi nhớ nhất là khi Jiu và Yuehui cuối cùng cũng đoàn tụ tại trạm Lollo Logistics, nơi họ gặp nhau lần đầu. Lời thoại của họ ở đó đã lột tả được bản chất của tình yêu. Đó không chỉ là sự lãng mạn, mà còn là cuộc sống đời thường chân thật khiến chúng ta cảm thấy trọn vẹn. Con người không giống như đôi chim huyền thoại. Dù Jiu rồi sẽ gặp ai đó, hay cố ép bản thân quên đi, nhưng vẫn có những điều luôn khiến anh nhớ về cô. Giống như cảnh cuối, khi anh ngồi trầm ngâm trong quán trà Jinzhou, nhìn chằm chằm vào bức tranh trên tường.</t>
         </is>
       </c>
@@ -12038,9 +12038,9 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Rating bởi [Deepsea Solitude] Cá Khô Trắng; Điểm: 10/10
+          <t>Đánh giá bởi [Deepsea Solitude] Cá Khô Trắng; Điểm: 10/10
 Dù không thể hiểu hết cảm xúc con người, nhưng điều đó không ngăn ta thưởng thức chúng. Một điểm tuyệt đối! Ngon lành, meo meo.
-Rating bởi [Scales of Death] Aurelia; Điểm: 8.3/10
+Đánh giá bởi [Scales of Death] Aurelia; Điểm: 8.3/10
 Biên tập phim này? Đỉnh cao. Nhịp điệu? Hoàn hảo. Những cảnh quay chậm, những góc quay cầm tay trên phố Jinzhou thực sự bắt trúng không khí. Khoảnh khắc ấy cứ ám ảnh tôi mãi. Các chuyển cảnh và góc máy, đặc biệt khi theo chân nhân vật, đều quá chuẩn. Còn cảnh quay ngược tại ga Lollo Logistics dưới mưa? Thật sự xuất sắc. Nó gợi mở cú twist bất ngờ mà không để lộ điều gì.
 Về cốt truyện, đây là một mẫu truyện kinh điển: hai nhân vật chính gặp gỡ, rồi chia xa, cuối cùng vòng tròn khép lại. Có phần dễ đoán và gọn gàng quá, nhưng thành thật mà nói, nó hiệu quả. Chân thật, và chính điều đó khiến nó chạm đến trái tim. Tôi cho 8.3 điểm vì đây là một viên ngọc quý trong thời đại điện ảnh hiện nay.</t>
         </is>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Trang đầu tiên của *Sổ tay Nhân viên Chi nhánh New*, do KU-Tata phát hành. Tài liệu này cung cấp cái nhìn tổng quan về mặt đất của Black Shores.
+          <t>Trang đầu tiên của *Sổ tay Nhân viên Chi nhánh Mới*, do KU-Tata phát hành. Tài liệu này cung cấp cái nhìn tổng quan về mặt đất của Black Shores.
 Là trung tâm nghiên cứu dự báo Lament và cứu rỗi thế giới, Black Shores còn được gọi là "điểm kỳ dị quan sát Lament". Trải qua nhiều nền văn minh, tổ chức này tập trung nghiên cứu Lament và các Hiện tượng Waveworn. Các thành viên Black Shores đi khắp thế giới thu thập mẫu Reverberation từ các vùng Lament, sử dụng Hệ thống Tethys để giải mã ngược. Mục tiêu của họ là tái tạo lại những điềm báo và quá trình của Lament nhằm xác định nguồn gốc ban đầu của nó. Bằng cách đưa một lượng lớn mẫu Reverberation vào hệ thống, họ hy vọng cải thiện độ chính xác của các dự báo về Lament và Hiện tượng Waveworn, giảm thiểu tổn thất cho đồng minh.
 Quần đảo Black Shores được xây dựng trên một khối Tacetite khổng lồ, giàu Năng lượng Tàn dư đa chiều, cung cấp năng lượng cho chi phí tính toán vô tận của Hệ thống Tethys. Ngoài ra, trường năng lượng rộng lớn do tần số của Tacetite tạo ra hình thành một lá chắn tự nhiên, che giấu Black Shores giữa biển khơi. Đối với những người ngoài tổ chức, việc vào Black Shores chỉ được phép thông qua lời mời, dưới sự hướng dẫn của Shorekeeper.</t>
         </is>
@@ -12251,10 +12251,10 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Report Sự cố Hạ Thân Nhiệt&lt;/i&gt;
+          <t>&lt;i&gt;Báo cáo Sự cố Hạ Thân Nhiệt&lt;/i&gt;
 Mỏ mới khảo sát mang ký hiệu T36E8 đã xuất hiện sương mù băng giá kèm theo âm thanh vo ve bất thường lan theo màn sương. Trước khi xác định được nguồn gốc của sương mù, mọi hoạt động khảo sát tại mỏ T36E8 đã bị đình chỉ.
 Sau khi sương mù băng giá xuất hiện, máy móc khai thác không thể đạt đến nhiệt độ vận hành hoặc phát cảnh báo an toàn. Nhiều thiết bị theo dõi sức khỏe tại hiện trường đã báo động tình trạng hạ thân nhiệt của công nhân. Đội Midnight Rangers đã tiến vào mỏ để thực hiện cứu hộ khẩn cấp.
-Các thợ mỏ bị thương đã được chuyển đến Khoa Y của Huaxu Academy. Để ứng phó, Bộ Phát triển đã điều Bộ phận Phòng vệ đến phong tỏa và kiểm soát hiện trường T36E8.
+Các thợ mỏ bị thương đã được chuyển đến Khoa Y của Học viện Huaxu. Để ứng phó, Bộ Phát triển đã điều Bộ phận Phòng vệ đến phong tỏa và kiểm soát hiện trường T36E8.
 Triệu chứng của các thợ mỏ bị ảnh hưởng bao gồm mê sảng, ảo giác và hạ thân nhiệt. Những tình trạng này, cùng với dấu hiệu sinh tồn bất thường, không đáp ứng với các phương pháp điều trị y tế tiêu chuẩn. Đánh giá sơ bộ chỉ ra khả năng xảy ra vụ tấn công liên quan đến TDs.</t>
         </is>
       </c>
@@ -12325,9 +12325,9 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Cẩm nang du lịch do Pioneer Association biên soạn, giới thiệu về suối nước nóng Hongzhen trên núi Cương Nghị.
+          <t>Cẩm nang du lịch do Hiệp Hội Tiên Phong biên soạn, giới thiệu về suối nước nóng Hongzhen trên núi Cương Nghị.
 [Sự chữa lành của yên bình] Hương Xuân
-Hương Xuân là một quán trọ suối nước nóng cổ kính nằm ở Hongzhen, Dodgep mình bên chân núi cạnh một suối nước nóng tự nhiên, nổi tiếng với phong cách kiến trúc độc đáo. Sau khi dòng chảy thời gian trên núi Cương Nghị được khôi phục, quán trọ cuối cùng cũng mở cửa đón khách bên ngoài. Ở đây, tuyết rơi lất phất hòa quyện cùng làn hơi nước bốc lên trong ánh đèn ấm áp, tạo nên bầu không khí thanh bình cho du khách đắm mình trong làn nước nóng, ngắm nhìn những dãy núi phủ tuyết trập trùng trên núi Cương Nghị. Trải nghiệm này hứa hẹn sẽ xua tan mọi mệt mỏi và căng thẳng! Nhiều du khách rời Hongzhen với cảm giác kinh ngạc và ngỡ ngàng, như thể họ vừa được chiêm ngưỡng một cõi tiên – biến Hương Xuân trở thành điểm đến suối nước nóng hàng đầu ở Huanglong!
+Hương Xuân là một quán trọ suối nước nóng cổ kính nằm ở Hongzhen, nép mình bên chân núi cạnh một suối nước nóng tự nhiên, nổi tiếng với phong cách kiến trúc độc đáo. Sau khi dòng chảy thời gian trên núi Cương Nghị được khôi phục, quán trọ cuối cùng cũng mở cửa đón khách bên ngoài. Ở đây, tuyết rơi lất phất hòa quyện cùng làn hơi nước bốc lên trong ánh đèn ấm áp, tạo nên bầu không khí thanh bình cho du khách đắm mình trong làn nước nóng, ngắm nhìn những dãy núi phủ tuyết trập trùng trên núi Cương Nghị. Trải nghiệm này hứa hẹn sẽ xua tan mọi mệt mỏi và căng thẳng! Nhiều du khách rời Hongzhen với cảm giác kinh ngạc và ngỡ ngàng, như thể họ vừa được chiêm ngưỡng một cõi tiên – biến Hương Xuân trở thành điểm đến suối nước nóng hàng đầu ở Huanglong!
 [Thử thách Trứng Suối Nóng] Trứng chần hoàn hảo
 Là quán trọ suối nước nóng lâu đời nhất trên Solaris-3, Hương Xuân cung cấp ẩm thực và chỗ ở phản ánh tinh hoa đích thực của núi Cương Nghị, nhận được sự tán thưởng từ mọi vị khách. Chủ quán là một người sành ăn, yêu đời và đam mê ẩm thực. Tận dụng tối đa nguồn suối nước nóng tự nhiên, ông đã sáng tạo ra phương pháp "hầm chậm suối nóng" độc đáo, trong đó thực phẩm được niêm phong trong lọ và ngâm trong suối nước nóng để nấu chín từ từ.
 Mỗi năm, Hương Xuân tổ chức Thử thách Trứng Suối Nóng, nơi các thí sinh tranh tài để nấu ra quả trứng hoàn hảo với lòng đỏ sền sệt như custard. Người chiến thắng được cho là sẽ nhận được một năm lưu trú miễn phí tại quán trọ!</t>
@@ -12399,7 +12399,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Một trang trong Sổ tay Nhân viên Chi nhánh New do KU-Tata phát hành. Nó cung cấp cái nhìn tổng quan về tầng ngầm của Black Shores.
+          <t>Một trang trong Sổ tay Nhân viên Chi nhánh Mới do KU-Tata phát hành. Nó cung cấp cái nhìn tổng quan về tầng ngầm của Black Shores.
 Tầng ngầm Black Shores là nơi không gian dữ liệu giao thoa với thực tại, còn gọi là Tethys' Deep.
 Nói cách khác, không gian ngầm của Black Shores chính là Hệ thống Tethys. Các Trạm Neo Không gian, thiết bị ổn định được đặt khắp bề mặt và tầng ngầm, đóng vai trò như bức tường lửa để duy trì sự cân bằng giữa vùng dữ liệu và thực tại, đảm bảo chúng không can thiệp lẫn nhau.
 Nếu các Trạm Neo Không gian gặp trục trặc, vùng dữ liệu trong Hệ thống Tethys có thể "xâm lấn" thực tại, gây ra các hiện tượng dị thường mà theo ghi chép bao gồm nhưng không giới hạn ở:
@@ -12471,9 +12471,9 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Tethys Hệ thống bao gồm hai thành phần chính: Dòng Data và Ma Trận Sao – một Siêu Máy Tính Bàn Cờ mô phỏng các thiên thể.
+          <t>Hệ Thống Tethys bao gồm hai thành phần chính: Dòng Dữ Liệu và Ma Trận Sao – một Siêu Máy Tính Bàn Cờ mô phỏng các thiên thể.
 Sử dụng dữ liệu của Lament để quan sát và phân tích cơ chế của nó, từ đó cảnh báo trước những lần Lament tái diễn trong tương lai, chính là nhiệm vụ của những "ngôi sao".
-Tuy nhiên, đây mới chỉ là bước khởi đầu trong việc ứng dụng và khám phá Tethys Hệ thống. Các nhà tư vấn của Black Shores đang nỗ lực hết sức để khai phá toàn bộ tiềm năng của nó.
+Tuy nhiên, đây mới chỉ là bước khởi đầu trong việc ứng dụng và khám phá Hệ Thống Tethys. Các nhà tư vấn của Black Shores đang nỗ lực hết sức để khai phá toàn bộ tiềm năng của nó.
 Người ta nói rằng người có quyền truy cập cao nhất trong Black Shores đã từng khai thác toàn bộ năng lực tính toán của Ma Trận Sao để mô phỏng tương lai của nền văn minh. Thế nhưng, nỗ lực này đã khiến hệ thống cạn kiệt tài nguyên đến mức gần như sụp đổ hoàn toàn.</t>
         </is>
       </c>
@@ -12550,10 +12550,10 @@
 Bao quanh bởi biển cả, người dân Ragunna sống hòa hợp với nước. Dù vì yêu thương hay sợ hãi, họ đều tôn kính nước sâu sắc. Theo một cách nào đó, điều này cũng phản ánh nỗi lo âu và sợ hãi của họ trước Đại Hồng Thủy, như lời tiên tri của Sentinel.
 Họ tổ chức nhiều nghi lễ để cầu nguyện với Sentinel, hy vọng rằng Sentinel sẽ dẫn dắt họ vượt qua những cơn sóng cuộc đời và cuối cùng đưa họ qua Đại Hồng Thủy.
 Các học giả của Giáo Đoàn cũng lấy cảm hứng từ những huyền thoại về Sentinel Imperator, phát triển cả một hệ thống lý thuyết về nước.
-[Lý thuyết I: Origin của thế giới là nước]
+[Lý thuyết I: Nguồn gốc của thế giới là nước]
 Nước hiện diện khắp mọi nơi và bao trùm vạn vật, tượng trưng cho sự vô tận. Nó là một thực thể có bản chất vô hạn. Mọi thứ đều bắt nguồn từ nước, kể cả sự hình thành của thế giới.
 [Lý thuyết II: Nước là chất lỏng, như sự vận động không ngừng của thủy triều]
-Trong chuyển động, nước phân chia thành những mặt đối lập: lạnh và nóng, khô và ướt, tạo nên thế giới. Sự vận động của nước chính là thủy triều. Mọi thứ sinh ra trong thủy triều và cuối cùng sẽ kết thúc trong Đại Hồng Thủy. Tuy nhiên, sự kết thúc này không có nghĩa là hủy diệt. Like mọi thứ đều bắt nguồn từ nước, kết thúc chỉ là sự trở về trong vòng tay của nước. Sự vận động này tạo nên một vòng tuần hoàn, cuối cùng hợp nhất mọi thứ trong biển cả. Từ sự hợp nhất này, con người lại được tách ra, rồi tái sinh như mầm non mùa xuân, trong một chu kỳ vô tận.</t>
+Trong chuyển động, nước phân chia thành những mặt đối lập: lạnh và nóng, khô và ướt, tạo nên thế giới. Sự vận động của nước chính là thủy triều. Mọi thứ sinh ra trong thủy triều và cuối cùng sẽ kết thúc trong Đại Hồng Thủy. Tuy nhiên, sự kết thúc này không có nghĩa là hủy diệt. Giống như mọi thứ đều bắt nguồn từ nước, kết thúc chỉ là sự trở về trong vòng tay của nước. Sự vận động này tạo nên một vòng tuần hoàn, cuối cùng hợp nhất mọi thứ trong biển cả. Từ sự hợp nhất này, con người lại được tách ra, rồi tái sinh như mầm non mùa xuân, trong một chu kỳ vô tận.</t>
         </is>
       </c>
     </row>
@@ -12641,10 +12641,10 @@
 [Lý thuyết IV: Nước là Sự Bao Dung]
 Chính bản chất bao dung này đã khiến Ragunna, dưới sự dẫn dắt của Giáo Đoàn, trở thành một thành phố chào đón những kẻ lưu vong từ mọi tầng lớp và ban cho họ quyền bình đẳng. Carnevale chính là biểu tượng của sự bao dung ấy. Người Ragunnesi từ khắp các hòn đảo tụ họp để tôn vinh quê hương và gia đình đã mất trong Lời Than Khóc. Họ mặc trang phục truyền thống, đeo mặt nạ tượng trưng cho tổ tiên và vật linh, biểu diễn đủ loại kịch nghệ. Sự đa dạng và bao dung chính là cốt lõi của những màn trình diễn trong Carnevale.
 [Lý thuyết V: Thống Nhất]
-Lấy cảm hứng từ bản chất bao dung của nước, The The Primus Fenrico khi lên nắm quyền đã phát triển học thuyết Thống Nhất và đưa nó vào Bộ Giáo Luật.
+Lấy cảm hứng từ bản chất bao dung của nước, Primus Fenrico khi lên nắm quyền đã phát triển học thuyết Thống Nhất và đưa nó vào Bộ Giáo Luật.
 Đối với những người lưu vong của Rinascita, hình thành sau Lời Than Khóc, tôn giáo không chỉ là nghi lễ trong Giáo Đoàn mà còn là sự kết tinh của khoa học, triết học, chính trị, bản sắc cá nhân và hy vọng về sự cứu rỗi. Nền văn minh Rinascita được neo giữ bởi niềm tin, nghĩa là tôn giáo không chỉ là sự theo đuổi cá nhân mà còn là chân lý phổ quát giải thích thế giới và xác định vị trí của mỗi người trong đó.
 Bất kỳ lý thuyết dị giáo nào làm suy yếu hay thách thức niềm tin này đều bị coi là lưỡi dao đâm vào trái tim của chân lý. Những tư tưởng như vậy đe dọa sự tồn tại của những người xung quanh và có nguy cơ xé nát cấu trúc xã hội, mang đến tai họa và hủy diệt cho thành phố bên bờ biển này.
-The The Primus tin rằng mỗi khi tư tưởng Phân Ly đạt đến đỉnh điểm, tai họa của Thủy Triều Hắc Ám sẽ giáng xuống từ trên cao, đe dọa sự tồn vong của Rinascita. Vì lý do đó, ngay cả Carnevale, biểu tượng của tinh thần bao dung, cũng phải nằm dưới sự giám sát của Giáo Đoàn.</t>
+Primus tin rằng mỗi khi tư tưởng Phân Ly đạt đến đỉnh điểm, tai họa của Thủy Triều Hắc Ám sẽ giáng xuống từ trên cao, đe dọa sự tồn vong của Rinascita. Vì lý do đó, ngay cả Carnevale, biểu tượng của tinh thần bao dung, cũng phải nằm dưới sự giám sát của Giáo Đoàn.</t>
         </is>
       </c>
     </row>
@@ -12712,9 +12712,9 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Ta từng đùa với một người bạn rằng nếu một ngày cậu bị truy nã khắp Solaris-3 vì những hành vi bất hợp pháp như bán khống hay buôn bán nợ, thì theo kinh nghiệm của ta, ngoài việc đào mộ chôn mình, lựa chọn tốt nhất là trốn vào Averardo Vault ở Rinascita. Chỉ cần chứng minh được giá trị của mình, gia tộc Montelli sẽ bảo vệ cậu—dù phải nhắm mắt làm ngơ. Họ thậm chí còn tự bỏ tiền bảo lãnh và thuê một đội luật sư quốc tế chuyên nghiệp cho cậu, với một điều kiện duy nhất: cậu phải xây dựng mối quan hệ kinh doanh vững chắc với họ.
-Tin ta đi, ta làm ăn với nhà Montelli nhiều lắm. Họ coi trọng cái gọi là "tinh thần hợp đồng" hơn hầu hết các doanh nhân khác.
-Hồi trẻ, ta không ưa nổi mấy người đảo ngang tàng đó. Họ không theo luật lệ nào, tràn đầy năng lượng và luôn nói thẳng. Chẳng giống gì người Rinascita ta biết, toàn múa hát và biểu diễn. Nhưng dần dần, ta nhận ra một đặc điểm mà họ có mà người khác không có. Họ luôn định giá mọi thứ ngay từ đầu. Nhà Montelli là những doanh nhân dễ hiểu nhất vì thế giới của họ chỉ vận hành theo một nguyên tắc duy nhất: hợp đồng. Và thứ duy nhất thúc đẩy nguyên tắc đó? Lợi nhuận.
+          <t>Tao từng đùa với một người bạn rằng nếu một ngày cậu bị truy nã khắp Solaris-3 vì những hành vi bất hợp pháp như bán khống hay buôn bán nợ, thì theo kinh nghiệm của tao, ngoài việc đào mộ chôn mình, lựa chọn tốt nhất là trốn vào Averardo Vault ở Rinascita. Chỉ cần chứng minh được giá trị của mình, gia tộc Montelli sẽ bảo vệ cậu—dù phải nhắm mắt làm ngơ. Họ thậm chí còn tự bỏ tiền bảo lãnh và thuê một đội luật sư quốc tế chuyên nghiệp cho cậu, với một điều kiện duy nhất: cậu phải xây dựng mối quan hệ kinh doanh vững chắc với họ.
+Tin tao đi, tao làm ăn với nhà Montelli nhiều lắm. Họ coi trọng cái gọi là "tinh thần hợp đồng" hơn hầu hết các doanh nhân khác.
+Hồi trẻ, tao không ưa nổi mấy người đảo ngang tàng đó. Họ không theo luật lệ nào, tràn đầy năng lượng và luôn nói thẳng. Chẳng giống gì người Rinascita tao biết, toàn múa hát và biểu diễn. Nhưng dần dần, tao nhận ra một đặc điểm mà họ có mà người khác không có. Họ luôn định giá mọi thứ ngay từ đầu. Nhà Montelli là những doanh nhân dễ hiểu nhất vì thế giới của họ chỉ vận hành theo một nguyên tắc duy nhất: hợp đồng. Và thứ duy nhất thúc đẩy nguyên tắc đó? Lợi nhuận.
 — Trích từ &lt;i&gt;Cách Kiếm Vỏ Sò Không Giới Hạn&lt;/i&gt;</t>
         </is>
       </c>
@@ -12783,7 +12783,7 @@
       <c r="M181" t="inlineStr">
         <is>
           <t>Chừng nào lợi nhuận dự kiến còn lớn hơn rủi ro, gia tộc Montelli sẽ làm mọi cách để hoàn thành hợp đồng. Họ không bao giờ từ chối bất kỳ thương vụ nào gõ cửa, và luôn giao hàng khi khách đã trả tiền. Đội ngũ của họ sở hữu một sức hút kỳ lạ, quy tụ những cá nhân bị tham vọng và danh vọng thôi thúc. Nhưng đừng mong nghe họ nói về đạo đức hay lòng trung thành—lợi nhuận là thước đo duy nhất.
-Khó mà hiểu nổi phải không? Một gia tộc nhúng tay vào công nghệ Echoes, thương mại toàn cầu, ngân hàng, vũ khí tư nhân, thậm chí từng thao túng tiền tệ, vậy mà họ không dựa vào huyết thống để duy trì đế chế. Hàng thập kỷ trôi qua, tài sản cất giấu trong Averardo Vault hẳn đã vượt xa trí tưởng tượng. Để bảo vệ nó, họ thậm chí nhập khẩu công nghệ chuyên dụng và nâng cấp Echoes thành những cỗ máy chiến tranh đáng gờm. Tin tôi đi, thưa các quý ông—dù tự tin đến đâu về khả năng của mình, đừng bao giờ mơ tưởng đến việc nhắm vào cái hầm đó.
+Khó mà hiểu nổi phải không? Một gia tộc nhúng tay vào công nghệ Echo, thương mại toàn cầu, ngân hàng, vũ khí tư nhân, thậm chí từng thao túng tiền tệ, vậy mà họ không dựa vào huyết thống để duy trì đế chế. Hàng thập kỷ trôi qua, tài sản cất giấu trong Hầm Averardo hẳn đã vượt xa trí tưởng tượng. Để bảo vệ nó, họ thậm chí nhập khẩu công nghệ chuyên dụng và nâng cấp Echo thành những cỗ máy chiến tranh đáng gờm. Tin tôi đi, thưa các quý ông—dù tự tin đến đâu về khả năng của mình, đừng bao giờ mơ tưởng đến việc nhắm vào cái hầm đó.
 —Trích từ &lt;i&gt;Cách Kiếm Vỏ Vô Hạn&lt;/i&gt;</t>
         </is>
       </c>
@@ -12933,8 +12933,8 @@
 Ôi, Ngài thật vĩ đại, Fenrico, Đấng Giác Ngộ! Ôi, Người thật vĩ đại, Sentinel Imperator!
 Những kẻ ngu ngốc bị đưa lên con tàu kia chính là những kẻ dị biệt, bị Ragunna đánh dấu, không thể hiểu được nguyên lý Thống Nhất mà Hội Dòng duy trì. Như câu nói trong vở kịch nổi tiếng: "Một là tất cả, tất cả là một." "Một" chính là lý tưởng của Ragunna, và những kẻ không thể hòa mình vào cái "một" duy nhất đó sẽ không bao giờ thực sự thuộc về "tất cả."
 Ghi chú: Đưa tên dị giáo này lên tàu ngay lập tức! Không được chậm trễ! Những lời lẽ phản nghịch, mỉa mai như thế phải bị xử lý!
-"Này, ngươi làm gì mà bị đày đến đây vậy?"
-"Ta à? Ta chỉ lặp lại những gì bọn chúng nói thôi..."</t>
+"Này, mày làm gì mà bị đày đến đây vậy?"
+"Tao à? Tao chỉ lặp lại những gì bọn chúng nói thôi..."</t>
         </is>
       </c>
     </row>
@@ -13170,8 +13170,8 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Là nhân viên chi nhánh Ragunna của Pioneer Association, tôi hiếm khi nhắc về quê hương với đồng nghiệp.
-Tôi đến từ một thị trấn nhỏ tên Egla, nơi hội tụ mọi định nghĩa của "thị trấn nhỏ"—giản dị, hơi lạc hậu, và yên tĩnh, ít nhất là vào ban ngày. Qua những chuyến công tác khắp nơi, tôi đã thấy không ít thị trấn như vậy. Hầu hết cuối cùng đều sáp nhập vào các thành phố kiên cố lớn hơn để tự vệ trước Echo hay Lament. Nhưng ít ai biết, lịch sử định cư của Egla gần như lâu đời ngang với Ragunna, và nó vẫn ngoan cố giữ nguyên bản sắc ban đầu.
+          <t>Là nhân viên chi nhánh Ragunna của Hiệp Hội Tiên Phong, tôi hiếm khi nhắc về quê hương với đồng nghiệp.
+Tôi đến từ một thị trấn nhỏ tên Egla, nơi hội tụ mọi định nghĩa của "thị trấn nhỏ"—giản dị, hơi lạc hậu, và yên tĩnh, ít nhất là vào ban ngày. Qua những chuyến công tác khắp nơi, tôi đã thấy không ít thị trấn như vậy. Hầu hết cuối cùng đều sáp nhập vào các thành phố kiên cố lớn hơn để tự vệ trước Tổ Tacet hay Lời Than Vãn. Nhưng ít ai biết, lịch sử định cư của Egla gần như lâu đời ngang với Ragunna, và nó vẫn ngoan cố giữ nguyên bản sắc ban đầu.
 Trong Hội, có một lời khuyên nổi tiếng: đừng bao giờ chọc giận các bậc trưởng lão ở Egla.
 Du khách đến Egla có thể gặp vài vị trưởng lão trông rất hoạt bát, có vẻ như những người bình thường—có thể là thị trưởng địa phương hay chủ quán trọ. Nhưng đằng sau vẻ ngoài khiêm tốn ấy, nhiều người từng là những nhân vật có ảnh hưởng, thậm chí là các Tín Đồ hoặc Tư Tế đã về hưu của Hội, từng phục vụ bên cạnh Primus, giải nghĩa các lời tiên tri, hay định hình giáo lý. Khi Ragunna còn đang trên đà phát triển, chính các vị trưởng lão này—hay tổ tiên của họ—đã đứng ở tiền tuyến, góp phần đặt nền móng cho thành phố. Sau những năm tháng phục vụ đầy vinh quang, họ trở về Egla, chọn sống những năm cuối đời tại nơi mọi thứ bắt đầu.</t>
         </is>
@@ -13243,8 +13243,8 @@
       <c r="M187" t="inlineStr">
         <is>
           <t>Rốt cuộc, điều gì khiến mọi người cứ quay về Thị trấn Egla nhỉ?
-Thật lòng mà nói, ta không tài nào hiểu nổi tâm lý của thế hệ đó.
-Lần cuối ta rời quê, ta thấy mấy ông già tụ tập trước một ngôi nhà bỏ hoang, cứ như đang làm lễ tưởng niệm vậy.
+Thật lòng mà nói, tao không tài nào hiểu nổi tâm lý của thế hệ đó.
+Lần cuối tao rời quê, tao thấy mấy ông già tụ tập trước một ngôi nhà bỏ hoang, cứ như đang làm lễ tưởng niệm vậy.
 Họ đứng đó im lặng hồi lâu, rồi một người lên tiếng, hồi tưởng lại quá khứ:
 "Ông bạn già ơi, thời gian đâu có quay ngược. Không thể cứ sống mãi trong những gì có thể đã xảy ra. Cậu phải hiểu rằng hiện tại chưa chắc đã tệ hơn quá khứ... thậm chí còn có thể tốt hơn... Cuối cùng, ta không cứu được đứa trẻ đó. Nhưng ta nên biết ơn vì đã cứu được phần lớn những người còn lại."</t>
         </is>
@@ -13477,11 +13477,11 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>10 Sự Thật Thú Vị Có Thể Bạn Đã Bỏ Lỡ Trong Bộ Phim Tài Liệu Lịch Sử Của Pioneer Association: Land Của Những Người Canh Gác!
-1. Tất cả cảnh quay về phép màu và huyền thoại đều được quay tại Fagaceae Peninsula, nơi duy nhất có loài Viscum Viride đặc trưng. Thú vị là, các nghiên cứu về dòng dõi thực vật cho thấy Viscum Viride rất có thể không phải loài bản địa của Rinascita.
-2. Trong những cảnh có Napoli Đệ Nhị, Dòng Tu Biển Sâu đã từ chối cho đoàn làm phim quay tại Nhà Thờ của họ. Thay vào đó, đoàn đã sử dụng tàn tích trên Fagaceae Peninsula để hoàn thành những cảnh này. Lý do từ chối là vì diễn viên đóng Napoli Đệ Nhị từng thủ vai một thương nhân yêu say đắm một Tu Sĩ trong một bộ phim tài liệu khác.
-3. Câu chuyện về sự trỗi dậy của gia tộc Fisalia được dựa trên truyền thuyết về một thương nhân giàu có đến từ New Federation, vì gia tộc Fisalia từ chối chia sẻ lịch sử của chính họ cho bộ phim tài liệu.
-4. Trong phim tài liệu, Thánh Nữ được miêu tả giúp dân làng hái trái cây khi còn nhỏ. Tuy nhiên, gần Egla Town không hề có cây ăn quả nào. Cảnh này thực chất được quay tại Fagaceae Peninsula.</t>
+          <t>10 Sự Thật Thú Vị Có Thể Bạn Đã Bỏ Lỡ Trong Bộ Phim Tài Liệu Lịch Sử Của Hiệp Hội Tiên Phong: Vùng Đất Của Những Người Canh Gác!
+1. Tất cả cảnh quay về phép màu và huyền thoại đều được quay tại Bán Đảo Fagaceae, nơi duy nhất có loài Viscum Viride đặc trưng. Thú vị là, các nghiên cứu về dòng dõi thực vật cho thấy Viscum Viride rất có thể không phải loài bản địa của Rinascita.
+2. Trong những cảnh có Napoli Đệ Nhị, Dòng Tu Biển Sâu đã từ chối cho đoàn làm phim quay tại Nhà Thờ của họ. Thay vào đó, đoàn đã sử dụng tàn tích trên Bán Đảo Fagaceae để hoàn thành những cảnh này. Lý do từ chối là vì diễn viên đóng Napoli Đệ Nhị từng thủ vai một thương nhân yêu say đắm một Tu Sĩ trong một bộ phim tài liệu khác.
+3. Câu chuyện về sự trỗi dậy của gia tộc Fisalia được dựa trên truyền thuyết về một thương nhân giàu có đến từ Liên Bang Mới, vì gia tộc Fisalia từ chối chia sẻ lịch sử của chính họ cho bộ phim tài liệu.
+4. Trong phim tài liệu, Thánh Nữ được miêu tả giúp dân làng hái trái cây khi còn nhỏ. Tuy nhiên, gần Thị Trấn Egla không hề có cây ăn quả nào. Cảnh này thực chất được quay tại Bán Đảo Fagaceae.</t>
         </is>
       </c>
     </row>
@@ -13637,17 +13637,16 @@
         <is>
           <t xml:space="preserve">
 ...
-Chánh Án: Nhân chứng, anh có khẳng định lời khai của nguyên đơn trong đơn kiện là sự thật không?
-Nhân Chứng: Không phải sự thật.
-Chánh Án: Trật tự!
-Chánh Án: Nhân chứng Acolyte Nicolo, ta hỏi lại, lời khai của nguyên đơn trong đơn kiện có chính xác không? Lưu ý, theo quy định của Tòa Án, bất kỳ mâu thuẫn nào trong lời khai của anh, nếu ảnh hưởng đến kết quả phiên tòa, đều có thể dẫn đến tội khai man!
-Nhân Chứng: Thưa quý tòa, trước Sentinel trên cao, tôi thừa nhận lời khai trước đây của mình là sai sự thật. Tôi đề nghị Tòa Án bảo vệ nhân chứng cho tôi và gia đình. Tôi khai rằng gia đình Montelli đã ép buộc tôi khai man trước tòa.
-Nguyên Đơn: Nicolo, anh bị điên à?! Gia đình Fisalias đã nói gì với anh trước phiên tòa?
-Bị Đơn: Hừ.
-Chánh Án: Trật tự!
-Chánh Án: Trật tự trong phòng xử! Với việc nhân chứng rút lại lời khai, Tòa Án Order sẽ tiếp tục quá trình thẩm vấn. Hội đồng thẩm phán sẽ xem xét các yêu cầu, bằng chứng và lời khai đã trình bày. Phiên tòa sẽ tiếp tục vào trưa mai, khi đó bản án sẽ được tuyên. Phiên tòa tạm ngừng.
-Thư Ký Tòa: Mọi người đứng dậy để chào đón chánh án và các thẩm phán rời đi. Các bên liên quan và khán giả có thể rời khỏi phòng xử án.
-</t>
+Chánh Án: Witness, do you affirm that the testimony provided by the plaintiff in the complaint is truthful?
+Witness: It is not truthful.
+Presiding Judge: Order!
+Presiding Judge: Witness Acolyte Nicolo, I ask you again, is the testimony provided by the plaintiff in the complaint accurate? Be advised, under the Tribunal's rules, any contradictions in your testimony, should they affect the outcome of this trial, may lead to charges of perjury!
+Witness: Your Honor, by the Sentinel above, I admit that my prior testimony was false. I request that the Tribunal provide witness protection for myself and my family. I testify that the Montelli family coerced me into making a false statement in court.
+Plaintiff: What madness is this, Nicolo?! What did the Fisalias say to you before the trial?
+Defendant: Heh.
+Presiding Judge: Order!
+Presiding Judge: Order in the court! Given the witness's retraction of his testimony, the Order Tribunal shall now resume the examination process. The panel of judges will review the claims, the evidence, and the testimony presented. The trial will reconvene tomorrow at noon, at which time the verdict will be rendered. The court is adjourned.
+Court Clerk: All rise for the presiding judge and judicial officers to depart. All parties and spectators may now exit the courtroom.</t>
         </is>
       </c>
     </row>
@@ -13717,10 +13716,10 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Sổ tay Nhân viên dành cho tất cả nhân viên của Averardo Vault. Dưới đây là nội dung trang đầu tiên:
-Chào mừng đến với Averardo Vault. Sự có mặt của các bạn mang đến nguồn năng lượng mới cho Kho Tàng, và chúng tôi chân thành mong đợi những thành tích xuất sắc từ các bạn.
-Theo nguyên tắc "sự thiêng liêng và bất khả xâm phạm của tài sản cá nhân", Averardo Vault lưu giữ một bộ sưu tập khổng lồ các Tacet Discord và tác phẩm nghệ thuật vô giá. Đây là nơi an toàn và bảo mật nhất ở Rinascita. Mỗi lời nói, hành động của các bạn đều phản ánh hình ảnh của Kho Tàng, và chúng tôi tin rằng cuốn sổ tay này sẽ giúp các bạn hiểu rõ hơn về Averardo Vault.
-Overview về Kho Tàng:
+          <t>Sổ tay Nhân viên dành cho tất cả nhân viên của Kho Tàng Averardo. Dưới đây là nội dung trang đầu tiên:
+Chào mừng đến với Kho Tàng Averardo. Sự có mặt của các bạn mang đến nguồn năng lượng mới cho Kho Tàng, và chúng tôi chân thành mong đợi những thành tích xuất sắc từ các bạn.
+Theo nguyên tắc "sự thiêng liêng và bất khả xâm phạm của tài sản cá nhân", Kho Tàng Averardo lưu giữ một bộ sưu tập khổng lồ các Tacet Discord và tác phẩm nghệ thuật vô giá. Đây là nơi an toàn và bảo mật nhất ở Rinascita. Mỗi lời nói, hành động của các bạn đều phản ánh hình ảnh của Kho Tàng, và chúng tôi tin rằng cuốn sổ tay này sẽ giúp các bạn hiểu rõ hơn về Kho Tàng Averardo.
+Tổng quan về Kho Tàng:
 Kho Tàng nằm ở phía đông Thành phố Ragunna, nơi lưu trữ vô số Tacet Discord và tác phẩm nghệ thuật. Kho Tàng được chia thành hai khu vực: Khu Quản Lý Cấp Cao, nằm trên một vực thẳm với tầm nhìn bao quát biển mây, và Khu Lưu Trữ Ngầm, nằm dưới biển mây và nối với khu vực trên bằng một tháp thang máy.
 Hệ thống an ninh của Kho Tàng bao gồm các Tacet Discord.</t>
         </is>
@@ -13934,7 +13933,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Hãy dấn thân vào những chuyến phiêu lưu để khám phá bí ẩn của tiếng vọng cổ xưa nơi vịnh biển hẻo lánh và săn tìm những viên ngọc trai trôi dạt vào bờ. Khi thủy triều rút dưới ánh hoàng hôn, hãy cùng những người dân thân thiện ở khu định cư Riccioli gần đó thưởng thức ly nước giải khát mát lạnh.
+          <t>Hãy dấn thân vào những chuyến phiêu lưu để khám phá bí ẩn của Echo cổ xưa nơi vịnh biển hẻo lánh và săn tìm những viên ngọc trai trôi dạt vào bờ. Khi thủy triều rút dưới ánh hoàng hôn, hãy cùng những người dân thân thiện ở khu định cư Riccioli gần đó thưởng thức ly nước giải khát mát lạnh.
 Và cuối cùng nhưng không kém phần quan trọng, đừng bỏ lỡ trải nghiệm câu cá đặc trưng của Riccioli!
 Đó chính là một thế giới thần tiên đầy sức sống, nơi vô vàn khả năng hòa quyện trong hương vị mặn mà của biển cả.
 Hãy đến với quần đảo Riccioli và để trái tim bạn rộn ràng khám phá những điều kỳ diệu mới mẻ của cuộc sống.</t>
@@ -14002,7 +14001,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Sản phẩm của một Quả Cầu Sonoro sụp đổ, xuất hiện khắp nơi trên thế giới. Nó ghi lại những ký ức nguyên vẹn của quá khứ. Nếu may mắn tìm thấy một cái, Relic Merchant sẽ sẵn lòng đổi lấy những món đồ giá trị.</t>
+          <t>Sản phẩm của một Sonoro Sphere sụp đổ, xuất hiện khắp nơi trên thế giới. Nó ghi lại những ký ức nguyên vẹn của quá khứ. Nếu may mắn tìm thấy một cái, Thương Nhân Di Vật sẽ sẵn lòng đổi lấy những món đồ giá trị.</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14066,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Một loại Discord bí ẩn tỏ ra đặc biệt quan tâm đến đồ vật của con người. Chúng xuất hiện khắp nơi trên thế giới. Nơi chúng dừng chân thường ẩn chứa những phần thưởng bất ngờ.</t>
+          <t>Một loại Tacet Discord bí ẩn tỏ ra đặc biệt quan tâm đến đồ vật của con người. Chúng xuất hiện khắp nơi trên thế giới. Nơi chúng dừng chân thường ẩn chứa những phần thưởng bất ngờ.</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14198,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ phải đối mặt với các đợt Vitreum Dancer lao tới. Dodge các đòn tấn công của chúng trong thời gian giới hạn để hoàn thành thử thách.</t>
+          <t>Trong Tactical Hologram: Vitreum Dancer, cậu sẽ phải đối mặt với các đợt Vitreum Dancer lao tới. Né tránh các đòn tấn công của chúng trong thời gian giới hạn để hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -14465,7 +14464,7 @@
       <c r="M204" t="inlineStr">
         <is>
           <t>Sản phẩm của một Sonoro Sphere sụp đổ, xuất hiện khắp nơi trên thế giới. Nó ghi lại những ký ức không bị méo mó của quá khứ.
-Dùng Grapple để móc và tiếp cận nhanh các Sonance Casket ở Ragunna. Những Plushie Echoes ở Garden Đồ Thất Lạc đang thu thập chúng—có lẽ đến thăm sẽ hé lộ thêm điều gì đó.</t>
+Dùng Grapple để móc và tiếp cận nhanh các Sonance Casket ở Ragunna. Những Plushie Echo ở Vườn Đồ Thất Lạc đang thu thập chúng—có lẽ đến thăm sẽ hé lộ thêm điều gì đó.</t>
         </is>
       </c>
     </row>
@@ -14995,7 +14994,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Vào mùa sinh sản ngắn ngủi, Bell Crab sẽ lột bỏ chiếc chuông đặc trưng để tìm bạn đời. Ngư dân đùa rằng chúng là "Bell-less Crab" trong thời gian này. Thịt của chúng được cho là trở nên vô cùng thơm ngon, thu hút những người sành ăn từ Ragunna đến thưởng thức món đặc sản theo mùa này.</t>
+          <t>Vào mùa sinh sản ngắn ngủi, Cua Chuông sẽ lột bỏ chiếc chuông đặc trưng để tìm bạn đời. Ngư dân đùa rằng chúng là "Cua Không Chuông" trong thời gian này. Thịt của chúng được cho là trở nên vô cùng thơm ngon, thu hút những người sành ăn từ Ragunna đến thưởng thức món đặc sản theo mùa này.</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15189,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Hầu hết các nhà sinh vật học ở Rinascita đều đồng ý rằng cái tên "Lươn Cầu Vồng" sẽ phù hợp hơn với sinh vật này so với "Yarn Eel" dựa trên vẻ ngoài sặc sỡ của chúng. Tuy nhiên, do bản tính nhút nhát, những con lươn này thường quấn vào nhau để sinh tồn. Dù "một đám Lươn Cầu Vồng nhút nhát" nghe có vẻ chính xác, nhưng "Yarn Eel" lại dễ đọc hơn nhiều.</t>
+          <t>Hầu hết các nhà sinh vật học ở Rinascita đều đồng ý rằng cái tên "Lươn Cầu Vồng" sẽ phù hợp hơn với sinh vật này so với "Lươn Sợi" dựa trên vẻ ngoài sặc sỡ của chúng. Tuy nhiên, do bản tính nhút nhát, những con lươn này thường quấn vào nhau để sinh tồn. Dù "một đám Lươn Cầu Vồng nhút nhát" nghe có vẻ chính xác, nhưng "Lươn Sợi" lại dễ đọc hơn nhiều.</t>
         </is>
       </c>
     </row>
@@ -15320,7 +15319,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Ở Riccioli Islands, những đứa trẻ nghịch ngợm thường bị dọa về Quái Vật Khổng Lồ Gulper, một loài săn mồi biển sâu được đồn thổi là bắt cóc trẻ hư vào ban đêm. Dù sinh vật này là nỗi ám ảnh tuổi thơ của bao đứa trẻ trên đảo, nhưng chính những Sob Blob, con mồi bất lực của nó, mới thực sự sống trong bóng tối của sự sợ hãi.</t>
+          <t>Ở Quần Đảo Riccioli, những đứa trẻ nghịch ngợm thường bị dọa về Quái Vật Khổng Lồ Gulper, một loài săn mồi biển sâu được đồn thổi là bắt cóc trẻ hư vào ban đêm. Dù sinh vật này là nỗi ám ảnh tuổi thơ của bao đứa trẻ trên đảo, nhưng chính những Sob Blob, con mồi bất lực của nó, mới thực sự sống trong bóng tối của sự sợ hãi.</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15514,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Với lớp vỏ gai sắc nhọn, Pricklecrab là kẻ săn mồi táo bạo và hung hãn dưới đáy biển sâu. Có người kể rằng một ngư dân đã đẩy lùi được Discord chỉ bằng cách Dodgem một con Pricklecrab vào nó. Quả là một sinh vật đầy mãnh lực.</t>
+          <t>Với lớp vỏ gai sắc nhọn, Pricklecrab là kẻ săn mồi táo bạo và hung hãn dưới đáy biển sâu. Có người kể rằng một ngư dân đã đẩy lùi được Tacet Discord chỉ bằng cách ném một con Pricklecrab vào nó. Quả là một sinh vật đầy mãnh lực.</t>
         </is>
       </c>
     </row>
@@ -15580,7 +15579,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Được mệnh danh là "Thiên Thần Biển", sinh vật mỏng manh này đẹp tựa tiên bướm. Nhiều người tin rằng nó là sứ giả của Cetus the Tidebreaker, có nhiệm vụ đưa những linh hồn lạc lối từ đáy đại dương trở về. Thế nhưng, với thân hình nhỏ bé như vậy, thật khó mà tin được nó có thể đảm đương sứ mệnh nặng nề đến thế.</t>
+          <t>Được mệnh danh là "Thiên Thần Biển", sinh vật mỏng manh này đẹp tựa tiên bướm. Nhiều người tin rằng nó là sứ giả của Cetus Kẻ Phá Thủy Triều, có nhiệm vụ đưa những linh hồn lạc lối từ đáy đại dương trở về. Thế nhưng, với thân hình nhỏ bé như vậy, thật khó mà tin được nó có thể đảm đương sứ mệnh nặng nề đến thế.</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15644,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Những bông hoa biển cổ này sinh trưởng mạnh mẽ ở Solaris, tạo nên mối liên kết hài hòa với Băng Seabed Snow. Dáng vẻ của chúng giống như những chiếc lông vũ trang trí trên mũ của các nghệ sĩ trong lễ hội Carnevale, nên mới có biệt danh là "Vương Miện Feather Ngôi Sao".</t>
+          <t>Những bông hoa biển cổ này sinh trưởng mạnh mẽ ở Solaris, tạo nên mối liên kết hài hòa với Băng Tuyết Dưới Đáy Biển. Dáng vẻ của chúng giống như những chiếc lông vũ trang trí trên mũ của các nghệ sĩ trong lễ hội Carnevale, nên mới có biệt danh là "Vương Miện Lông Vũ Ngôi Sao".</t>
         </is>
       </c>
     </row>
@@ -15710,7 +15709,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Bóng Ma Styx, loài sứa độc được gia tộc Fisalia yêu quý, hoàn toàn đối lập với Cetus the Tidebreaker. Trong khi Cetus được tôn kính vì đưa linh hồn thủy thủ về thế giới bên kia, Bóng Ma Styx lại bị đồn là đưa những linh hồn lạc lối xuống Địa Ngục của Chúa Tể Mực, nơi chúng mãi mãi bị giam cầm.</t>
+          <t>Bóng Ma Styx, loài sứa độc được gia tộc Fisalia yêu quý, hoàn toàn đối lập với Cetus Kẻ Phá Thủy Triều. Trong khi Cetus được tôn kính vì đưa linh hồn thủy thủ về thế giới bên kia, Bóng Ma Styx lại bị đồn là đưa những linh hồn lạc lối xuống Địa Ngục của Chúa Tể Mực, nơi chúng mãi mãi bị giam cầm.</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15904,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Một sinh vật huyền thoại, một trong những bá chủ của sinh vật biển tại quần đảo Riccioli. Nguồn gốc, cấu trúc và sức mạnh của cỗ máy bí ẩn này vẫn còn là điều bí ẩn. Liệu nó có đến từ một thế giới nơi con người có thể biến thành máy móc, robot biết nói, tàu bay thống trị bầu trời và cá được làm bằng sắt? Gì cơ? Cậu muốn biết tại sao biển ở đó lại đỏ à?</t>
+          <t>Một sinh vật huyền thoại, một trong những bá chủ của sinh vật biển tại quần đảo Riccioli. Nguồn gốc, cấu trúc và sức mạnh của cỗ máy bí ẩn này vẫn còn là điều bí ẩn. Liệu nó có đến từ một thế giới nơi con người có thể biến thành máy móc, robot biết nói, tàu bay thống trị bầu trời và cá được làm bằng sắt? Gì? Cậu muốn biết tại sao biển ở đó lại đỏ à?</t>
         </is>
       </c>
     </row>
@@ -16035,7 +16034,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Thuyền trưởng Ahab và Bertoli, nhà sinh vật học của Pioneer Association, từng có một cuộc tranh cãi nảy lửa về tên gọi của loài cá này. Ahab khăng khăng rằng sở thích phơi nắng của nó xứng đáng được gọi là "Sunfish", thì Bertoli đáp lại: "Vậy sao không gọi luôn là 'Cá Khô Dẹt' cho rồi?"</t>
+          <t>Thuyền trưởng Ahab và Bertoli, nhà sinh vật học của Hiệp hội Pioneer, từng có một cuộc tranh cãi nảy lửa về tên gọi của loài cá này. Ahab khăng khăng rằng sở thích phơi nắng của nó xứng đáng được gọi là "Cá Mặt Trời", thì Bertoli đáp lại: "Vậy sao không gọi luôn là 'Cá Khô Dẹt' cho rồi?"</t>
         </is>
       </c>
     </row>
@@ -16165,7 +16164,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Là kẻ săn mồi hàng đầu trong vùng biển quanh quần đảo Riccioli, Lancetfish nổi tiếng với tính khí nóng nảy. Một khi đã ngoạm chặt con mồi, nó sẽ không bao giờ buông tha, nuốt chửng nạn nhân một cách trọn vẹn. Thói quen này đã dẫn đến việc thường xuyên bắt được những con Lancetfish chết vì cố nuốt chửng Trombone Ammonoid – kể cả lớp vỏ cứng.</t>
+          <t>Là kẻ săn mồi hàng đầu trong vùng biển quanh quần đảo Riccioli, Cá Kiếm nổi tiếng với tính khí nóng nảy. Một khi đã ngoạm chặt con mồi, nó sẽ không bao giờ buông tha, nuốt chửng nạn nhân một cách trọn vẹn. Thói quen này đã dẫn đến việc thường xuyên bắt được những con Cá Kiếm chết vì cố nuốt chửng Trombone Ammonoid – kể cả lớp vỏ cứng.</t>
         </is>
       </c>
     </row>
@@ -16295,7 +16294,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Các họa sĩ ở Ragunna từng cố chiết xuất sắc màu rực rỡ từ cá Chuột Đuôi Cầu Vồng để dùng trong tranh, nhưng đành từ bỏ khi sắc tố không thể pha trộn. Loài cá này luôn mang theo con non khi săn mồi và bảo vệ chúng quyết liệt. Nếu đàn con gặp nguy, nó sẽ phản công không chút do dự, thậm chí lật úp cả thuyền đánh cá—vì thế mới có biệt danh "Iron Lady".</t>
+          <t>Các họa sĩ ở Ragunna từng cố chiết xuất sắc màu rực rỡ từ cá Chuột Đuôi Cầu Vồng để dùng trong tranh, nhưng đành từ bỏ khi sắc tố không thể pha trộn. Loài cá này luôn mang theo con non khi săn mồi và bảo vệ chúng quyết liệt. Nếu đàn con gặp nguy, nó sẽ phản công không chút do dự, thậm chí lật úp cả thuyền đánh cá—vì thế mới có biệt danh "Quý Bà Thép".</t>
         </is>
       </c>
     </row>
@@ -16555,7 +16554,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Một sinh vật huyền thoại, một trong những bá chủ của sinh vật biển tại quần đảo Riccioli. Truyền thuyết kể rằng trong chuyến hành hương của Napolis Đệ Nhị, một cơn bão nổi lên. Để dẹp yên giông tố, một bảo vật thiêng màu hồng được Dodgem xuống biển dữ, khiến mặt nước trở lại yên bình. Một con cá đuối bình thường tình cờ bơi qua bảo vật và được nhuốm màu hồng của nó.</t>
+          <t>Một sinh vật huyền thoại, một trong những bá chủ của sinh vật biển tại quần đảo Riccioli. Truyền thuyết kể rằng trong chuyến hành hương của Napolis Đệ Nhị, một cơn bão nổi lên. Để dẹp yên giông tố, một bảo vật thiêng màu hồng được ném xuống biển dữ, khiến mặt nước trở lại yên bình. Một con cá đuối bình thường tình cờ bơi qua bảo vật và được nhuốm màu hồng của nó.</t>
         </is>
       </c>
     </row>
@@ -17017,7 +17016,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Vào mùa sinh sản ngắn ngủi, Bell Crab sẽ lột bỏ chiếc chuông đặc trưng để tìm bạn đời. Ngư dân đùa rằng chúng là "Bell-less Crab" trong thời gian này. Thịt của chúng được cho là trở nên vô cùng thơm ngon, thu hút những người sành ăn từ Ragunna đến thưởng thức món đặc sản theo mùa này.
+          <t>Vào mùa sinh sản ngắn ngủi, Cua Chuông sẽ lột bỏ chiếc chuông đặc trưng để tìm bạn đời. Ngư dân đùa rằng chúng là "Cua Không Chuông" trong thời gian này. Thịt của chúng được cho là trở nên vô cùng thơm ngon, thu hút những người sành ăn từ Ragunna đến thưởng thức món đặc sản theo mùa này.
 &lt;color=#b9b9b9&gt;Biến thể đột biến này dường như đã bị ảnh hưởng bởi xung đột giữa Sentinel và Threnodian. Ngoại hình biến đổi của nó khác biệt rõ rệt so với loại hoang dã, trở thành một món đồ sưu tầm hấp dẫn với mức giá không hề rẻ.&lt;/color&gt;</t>
         </is>
       </c>
@@ -17218,7 +17217,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Chúng là cá à? Đúng, đúng rồi. Ta nấu xong chưa nhỉ? Chưa, chưa...
+          <t>Chúng là cá à? Đúng, đúng rồi. Tao nấu xong chưa nhỉ? Chưa, chưa...
 &lt;color=#b9b9b9&gt;Hình dạng của chúng dường như đã bị bóp méo bởi sự xung đột giữa Sentinel và Threnodian. Ngoại hình biến đổi của chúng khác xa so với hình dạng nguyên thủy, trở thành một món hàng hiếm có giá trị lớn đối với những nhà sưu tầm sẵn sàng chi trả số tiền khổng lồ.&lt;/color&gt;</t>
         </is>
       </c>
@@ -17486,7 +17485,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ở Riccioli Islands, những đứa trẻ nghịch ngợm thường bị dọa về Quái Vật Khổng Lồ Gulper, một loài săn mồi biển sâu được đồn thổi là bắt cóc trẻ hư vào ban đêm. Dù sinh vật này là nỗi ám ảnh tuổi thơ của bao đứa trẻ trên đảo, nhưng chính những Sob Blob, con mồi bất lực của nó, mới thực sự sống trong bóng tối của sự sợ hãi.
+          <t>Ở Quần Đảo Riccioli, những đứa trẻ nghịch ngợm thường bị dọa về Quái Vật Khổng Lồ Gulper, một loài săn mồi biển sâu được đồn thổi là bắt cóc trẻ hư vào ban đêm. Dù sinh vật này là nỗi ám ảnh tuổi thơ của bao đứa trẻ trên đảo, nhưng chính những Sob Blob, con mồi bất lực của nó, mới thực sự sống trong bóng tối của sự sợ hãi.
 &lt;color=#b9b9b9&gt;Biến thể đột biến này dường như đã bị ảnh hưởng bởi những xung đột giữa Sentinel và Threnodian. Ngoại hình biến đổi của nó khác biệt rõ rệt so với loại hoang dã, trở thành một "báu vật" hấp dẫn cho những tay sưu tầm sẵn sàng chi trả giá cao.&lt;/color&gt;</t>
         </is>
       </c>
@@ -17821,7 +17820,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Với lớp vỏ gai sắc nhọn, Pricklecrab là kẻ săn mồi táo bạo và hung hãn dưới đáy biển sâu. Có người kể rằng một ngư dân đã đẩy lùi được Discord chỉ bằng cách Dodgem một con Pricklecrab vào nó. Quả là một sinh vật đầy mãnh lực.
+          <t>Với lớp vỏ gai sắc nhọn, Pricklecrab là kẻ săn mồi táo bạo và hung hãn dưới đáy biển sâu. Có người kể rằng một ngư dân đã đẩy lùi được Tacet Discord chỉ bằng cách ném một con Pricklecrab vào nó. Quả là một sinh vật đầy mãnh lực.
 &lt;color=#b9b9b9&gt;Biến thể đột biến này dường như đã bị ảnh hưởng bởi những xung đột giữa Sentinel và Threnodian. Ngoại hình thay đổi của nó khác biệt rõ rệt so với loại hoang dã, trở thành một món đồ sưu tầm hấp dẫn cho những ai sẵn sàng trả giá cao.&lt;/color&gt;</t>
         </is>
       </c>
@@ -17888,7 +17887,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Được mệnh danh là "Thiên Thần Biển", sinh vật mỏng manh này đẹp tựa tiên bướm. Nhiều người tin rằng nó là sứ giả của Cetus the Tidebreaker, có nhiệm vụ đưa những linh hồn lạc lối từ đáy đại dương trở về. Thế nhưng, với thân hình nhỏ bé như vậy, thật khó mà tin được nó có thể đảm đương sứ mệnh nặng nề đến thế.
+          <t>Được mệnh danh là "Thiên Thần Biển", sinh vật mỏng manh này đẹp tựa tiên bướm. Nhiều người tin rằng nó là sứ giả của Cetus Kẻ Phá Thủy Triều, có nhiệm vụ đưa những linh hồn lạc lối từ đáy đại dương trở về. Thế nhưng, với thân hình nhỏ bé như vậy, thật khó mà tin được nó có thể đảm đương sứ mệnh nặng nề đến thế.
 &lt;color=#b9b9b9&gt;Biến thể đột biến này dường như đã chịu ảnh hưởng từ sự xung đột giữa Sentinel và Threnodian. Ngoại hình biến đổi của nó khác biệt rõ rệt so với loại hoang dã, trở thành món hàng hiếm có giá trị lớn trong mắt các nhà sưu tầm sẵn sàng chi trả số tiền khổng lồ.&lt;/color&gt;</t>
         </is>
       </c>
@@ -17955,7 +17954,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Những bông hoa biển cổ này sinh trưởng mạnh mẽ ở Solaris, tạo nên mối liên kết hài hòa với Băng Seabed Snow. Dáng vẻ của chúng giống như những chiếc lông vũ trang trí trên mũ của các nghệ sĩ trong lễ hội Carnevale, nên mới có biệt danh là "Vương Miện Feather Ngôi Sao".
+          <t>Những bông hoa biển cổ này sinh trưởng mạnh mẽ ở Solaris, tạo nên mối liên kết hài hòa với Băng Tuyết Dưới Đáy Biển. Dáng vẻ của chúng giống như những chiếc lông vũ trang trí trên mũ của các nghệ sĩ trong lễ hội Carnevale, nên mới có biệt danh là "Vương Miện Lông Vũ Ngôi Sao".
 &lt;color=#b9b9b9&gt;Biến thể đột biến này dường như đã chịu ảnh hưởng từ sự xung đột giữa Sentinel và Threnodian. Ngoại hình biến đổi của nó khác biệt rõ rệt so với loại hoang dã, trở thành một món đồ sưu tầm hấp dẫn cho những tay chơi sẵn sàng chi trả giá cao.&lt;/color&gt;</t>
         </is>
       </c>
@@ -18022,7 +18021,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Bóng Ma Styx, loài sứa độc được gia tộc Fisalia yêu quý, hoàn toàn đối lập với Cetus the Tidebreaker. Trong khi Cetus được tôn kính vì đưa linh hồn thủy thủ về thế giới bên kia, Bóng Ma Styx lại bị đồn là đưa những linh hồn lạc lối xuống Địa Ngục của Chúa Tể Mực, nơi chúng mãi mãi bị giam cầm.
+          <t>Bóng Ma Styx, loài sứa độc được gia tộc Fisalia yêu quý, hoàn toàn đối lập với Cetus Kẻ Phá Thủy Triều. Trong khi Cetus được tôn kính vì đưa linh hồn thủy thủ về thế giới bên kia, Bóng Ma Styx lại bị đồn là đưa những linh hồn lạc lối xuống Địa Ngục của Chúa Tể Mực, nơi chúng mãi mãi bị giam cầm.
 &lt;color=#b9b9b9&gt;Biến thể đột biến này dường như bị ảnh hưởng bởi xung đột giữa Sentinel và Threnodian. Ngoại hình biến đổi của nó khác biệt rõ rệt so với loại hoang dã, trở thành vật sưu tầm hấp dẫn cho những kẻ sẵn sàng chi mạnh tay.&lt;/color&gt;</t>
         </is>
       </c>
@@ -18289,7 +18288,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Một sinh vật huyền thoại, một trong những bá chủ của sinh vật biển tại quần đảo Riccioli. Nguồn gốc, cấu trúc và sức mạnh của cỗ máy bí ẩn này vẫn còn là điều bí ẩn. Liệu nó có đến từ một thế giới nơi con người có thể biến thành máy móc, robot biết nói, tàu bay thống trị bầu trời và cá được làm bằng sắt? Gì cơ? Cậu muốn biết tại sao biển ở đó lại đỏ à?</t>
+          <t>Một sinh vật huyền thoại, một trong những bá chủ của sinh vật biển tại quần đảo Riccioli. Nguồn gốc, cấu trúc và sức mạnh của cỗ máy bí ẩn này vẫn còn là điều bí ẩn. Liệu nó có đến từ một thế giới nơi con người có thể biến thành máy móc, robot biết nói, tàu bay thống trị bầu trời và cá được làm bằng sắt? Gì? Cậu muốn biết tại sao biển ở đó lại đỏ à?</t>
         </is>
       </c>
     </row>
@@ -18422,7 +18421,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Thuyền trưởng Ahab và Bertoli, nhà sinh vật học của Pioneer Association, từng có một cuộc tranh cãi nảy lửa về tên gọi của loài cá này. Ahab khăng khăng rằng sở thích phơi nắng của nó xứng đáng được gọi là "Sunfish", thì Bertoli đáp lại: "Vậy sao không gọi luôn là 'Cá Khô Dẹt' cho rồi?"
+          <t>Thuyền trưởng Ahab và Bertoli, nhà sinh vật học của Hiệp hội Pioneer, từng có một cuộc tranh cãi nảy lửa về tên gọi của loài cá này. Ahab khăng khăng rằng sở thích phơi nắng của nó xứng đáng được gọi là "Cá Mặt Trời", thì Bertoli đáp lại: "Vậy sao không gọi luôn là 'Cá Khô Dẹt' cho rồi?"
 &lt;color=#b9b9b9&gt;Biến thể đột biến này dường như đã bị ảnh hưởng bởi những xung đột giữa Sentinel và Threnodian. Ngoại hình biến đổi của nó khác biệt rõ rệt so với loại hoang dã, trở thành một món hời hấp dẫn cho những nhà sưu tầm sẵn sàng chi trả giá cao.&lt;/color&gt;</t>
         </is>
       </c>
@@ -18556,7 +18555,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Là kẻ săn mồi hàng đầu trong vùng biển quanh quần đảo Riccioli, Lancetfish nổi tiếng với tính khí nóng nảy. Một khi đã ngoạm chặt con mồi, nó sẽ không bao giờ buông tha, nuốt chửng nạn nhân một cách trọn vẹn. Thói quen này đã dẫn đến việc thường xuyên bắt được những con Lancetfish chết vì cố nuốt chửng Trombone Ammonoid – kể cả lớp vỏ cứng.
+          <t>Là kẻ săn mồi hàng đầu trong vùng biển quanh quần đảo Riccioli, Cá Kiếm nổi tiếng với tính khí nóng nảy. Một khi đã ngoạm chặt con mồi, nó sẽ không bao giờ buông tha, nuốt chửng nạn nhân một cách trọn vẹn. Thói quen này đã dẫn đến việc thường xuyên bắt được những con Cá Kiếm chết vì cố nuốt chửng Trombone Ammonoid – kể cả lớp vỏ cứng.
 &lt;color=#b9b9b9&gt;Biến thể đột biến này dường như đã bị ảnh hưởng bởi những xung đột giữa Sentinel và Threnodian. Ngoại hình biến đổi của nó khác biệt rõ rệt so với loại hoang dã, trở thành một chiến lợi phẩm hấp dẫn cho những nhà sưu tầm sẵn sàng chi trả một khoản tiền lớn.&lt;/color&gt;</t>
         </is>
       </c>
@@ -19040,21 +19039,21 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>[Giới thiệu]
-Sau một thập kỷ chờ đợi, Carnevale được mong đợi từ lâu đã thổi bùng ngọn lửa đam mê không ngừng tắt.
-Thành phố Nước vừa hé lộ một góc bí mật. Đây chính là thời điểm tốt nhất để căng buồm, lướt theo gió và khám phá những ngóc ngách chưa ai đặt chân đến của vùng đất bí ẩn này.
-Khi bức màn thế giới được vén lên, một cuộc thám hiểm mới đang gọi tên—còn chờ gì nữa? Hãy bắt đầu phiêu lưu ngay!
-[Điều kiện tham gia]
-Đạt Cấp Liên Minh 22 và mở khóa Công Cụ: Bay Lượn.
-[Quy tắc sự kiện]
-1. Trong sự kiện, bạn có thể mời người chơi khác tham gia Overdash Challenge ở Chế độ Hợp tác. Người về đích đầu tiên sẽ thắng.
-2. Khi người chơi đầu tiên hoàn thành, thử thách sẽ bước vào giai đoạn nước rút 20 giây. Sau khi giai đoạn này kết thúc, kết quả sẽ được chốt.
-3. Chiến đấu bị vô hiệu hóa trong thử thách. Người chơi phải đi theo chỉ dẫn để hoàn thành.
-4. Points cuối gồm hai phần: Points Hoàn thành Đường đua và Points Ranking:
-I. Points Hoàn thành Đường đua được tính khi đến các điểm kiểm tra trên đường đua.
-II. Points Ranking được tính dựa trên thứ tự về đích của người chơi.
-[Lưu ý]
-Resonators có chiều cao khác nhau sẽ chạy với tốc độ khác nhau.</t>
+          <t>Về sự kiện
+Sau một thập kỷ chờ đợi, Carnevale huyền thoại cuối cùng đã trở lại, thổi bùng ngọn lửa đam mê không ngừng tắt.
+Thành phố Nước vừa hé lộ một góc bí ẩn của mình. Đây chính là thời điểm hoàn hảo để căng buồm, lướt theo gió và khám phá những góc khuất chưa ai đặt chân tới của vùng đất kỳ bí này.
+Khi bức màn thế giới dần được vén lên, một cuộc phiêu lưu mới đang chờ đón—còn chần chừ gì nữa? Hãy bắt đầu ngay thôi!
+Điều kiện tham gia
+Đạt Cấp Liên Minh 22 và mở khóa Tiện ích: Bay.
+Quy tắc sự kiện
+1. Trong sự kiện, bạn có thể mời người chơi khác tham gia Thử thách Overdash ở Chế độ Hợp tác. Ai về đích trước sẽ là người chiến thắng.
+2. Khi người chơi đầu tiên về đích, thử thách sẽ bước vào giai đoạn nước rút 20 giây. Sau khi giai đoạn này kết thúc, kết quả sẽ được xác định.
+3. Chiến đấu bị vô hiệu hóa trong thử thách. Người chơi phải đi theo các điểm đánh dấu để hoàn thành thử thách.
+4. Điểm cuối cùng bao gồm hai phần: Điểm Hoàn Thành Đường Đua và Điểm Xếp Hạng:
+I. Điểm Hoàn Thành Đường Đua được tính khi đến các điểm kiểm tra đã chỉ định trên đường đua.
+II. Điểm Xếp Hạng được tính dựa trên thứ tự về đích của người chơi.
+Lưu ý
+Resonator ở các độ cao khác nhau sẽ có tốc độ di chuyển khác nhau.</t>
         </is>
       </c>
     </row>
@@ -20632,7 +20631,7 @@
       <c r="M297" t="inlineStr">
         <is>
           <t>Bạn đã nắm vững bí quyết đánh bắt quanh quần đảo Riccioli, nhờ đó có thể &lt;color=#e7a60b&gt;bán&lt;/color&gt; hải sản với &lt;color=#e7a60b&gt;giá hời&lt;/color&gt; hơn.
-&lt;color=#929292&gt;Nhờ nghiên cứu Hướng dẫn Fishing Rinascita, bạn đã hiểu rõ đặc tính của các loài sinh vật biển. Giờ đây, việc bắt được những mẻ cá chất lượng cao trở nên dễ dàng hơn.&lt;/color&gt;</t>
+&lt;color=#929292&gt;Nhờ nghiên cứu Hướng dẫn Câu cá Rinascita, bạn đã hiểu rõ đặc tính của các loài sinh vật biển. Giờ đây, việc bắt được những mẻ cá chất lượng cao trở nên dễ dàng hơn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20698,7 +20697,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Nghiên cứu Hướng dẫn Fishing Rinascita sẽ giúp cậu trở thành một ngư dân lão luyện, kiếm được nhiều &lt;color=#e7a60b&gt;Đồng Tiền Fishing&lt;/color&gt; hơn từ các &lt;color=#e7a60b&gt;Requests&lt;/color&gt;.
+          <t>Nghiên cứu Hướng dẫn Câu cá Rinascita sẽ giúp cậu trở thành một ngư dân lão luyện, kiếm được nhiều &lt;color=#e7a60b&gt;Đồng Tiền Câu Cá&lt;/color&gt; hơn từ các &lt;color=#e7a60b&gt;Yêu Cầu&lt;/color&gt;.
 &lt;color=#929292&gt;Người ta vẫn bảo "có công mài sắt có ngày nên kim", và ngay cả ở vùng đất xa lạ này, cậu đã trở thành một chuyên gia câu cá chính hiệu rồi đấy.&lt;/color&gt;</t>
         </is>
       </c>
@@ -20765,8 +20764,8 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Nghiên cứu Hướng dẫn Fishing Rinascita sẽ giúp cậu trở thành một ngư dân lão luyện, kiếm được nhiều &lt;color=#e7a60b&gt;Đồng Tiền Fishing&lt;/color&gt; hơn từ các &lt;color=#e7a60b&gt;Requests&lt;/color&gt;.
-&lt;color=#929292&gt;Ngư Dân Legendary, Thợ Săn Biển Áo Black... Những danh hiệu này đi kèm với những yêu cầu cực kỳ thử thách, nhưng phần thưởng cũng hậu hĩnh không kém.&lt;/color&gt;</t>
+          <t>Nghiên cứu Hướng dẫn Câu cá Rinascita sẽ giúp cậu trở thành một ngư dân lão luyện, kiếm được nhiều &lt;color=#e7a60b&gt;Đồng Tiền Câu Cá&lt;/color&gt; hơn từ các &lt;color=#e7a60b&gt;Yêu Cầu&lt;/color&gt;.
+&lt;color=#929292&gt;Ngư Dân Huyền Thoại, Thợ Săn Biển Áo Đen... Những danh hiệu này đi kèm với những yêu cầu cực kỳ thử thách, nhưng phần thưởng cũng hậu hĩnh không kém.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20832,7 +20831,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Những lời cầu nguyện thất lạc từ mảnh kinh thư tìm thấy trên quần đảo Riccioli. Enhance &lt;color=#e7a60b&gt;Độ Bền&lt;/color&gt; cho thân tàu Rachel.
+          <t>Những lời cầu nguyện thất lạc từ mảnh kinh thư tìm thấy trên quần đảo Riccioli. Tăng cường &lt;color=#e7a60b&gt;Độ Bền&lt;/color&gt; cho thân tàu Rachel.
 &lt;color=#929292&gt;"Nguyện đức tin che chở chúng ta, củng cố con tàu."&lt;/color&gt;</t>
         </is>
       </c>
@@ -21033,7 +21032,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Kỹ thuật tái chế được ghi lại trong Guide Fishing Rinascita, giúp bạn thu hồi thêm &lt;color=#e7a60b&gt;vật liệu&lt;/color&gt; từ việc xử lý tài nguyên.
+          <t>Kỹ thuật tái chế được ghi lại trong Hướng Dẫn Câu Cá Rinascita, giúp bạn thu hồi thêm &lt;color=#e7a60b&gt;vật liệu&lt;/color&gt; từ việc xử lý tài nguyên.
 &lt;color=#929292&gt;Đối với cư dân đảo xa đất liền, mỗi tài nguyên đều phải được sử dụng một cách khôn ngoan và tiết kiệm.&lt;/color&gt;</t>
         </is>
       </c>
@@ -21100,7 +21099,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Kỹ thuật tái chế được ghi lại trong Guide Fishing Rinascita, giúp bạn thu hồi thêm nhiều &lt;color=#e7a60b&gt;vật liệu&lt;/color&gt; từ việc xử lý tài nguyên.
+          <t>Kỹ thuật tái chế được ghi lại trong Hướng Dẫn Câu Cá Rinascita, giúp bạn thu hồi thêm nhiều &lt;color=#e7a60b&gt;vật liệu&lt;/color&gt; từ việc xử lý tài nguyên.
 &lt;color=#929292&gt;Đối với cư dân đảo xa đất liền, mỗi tài nguyên đều phải được sử dụng một cách khôn ngoan và tiết kiệm.&lt;/color&gt;</t>
         </is>
       </c>
@@ -21167,7 +21166,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Kỹ thuật tái chế được ghi lại trong Guide Fishing Rinascita, giúp bạn thu hồi thêm nhiều &lt;color=#e7a60b&gt;vật liệu&lt;/color&gt; từ việc xử lý tài nguyên.
+          <t>Kỹ thuật tái chế được ghi lại trong Hướng Dẫn Câu Cá Rinascita, giúp bạn thu hồi thêm nhiều &lt;color=#e7a60b&gt;vật liệu&lt;/color&gt; từ việc xử lý tài nguyên.
 &lt;color=#929292&gt;Đối với cư dân đảo xa đất liền, mỗi tài nguyên đều phải được sử dụng một cách khôn ngoan và tiết kiệm.&lt;/color&gt;</t>
         </is>
       </c>
@@ -21368,7 +21367,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Một thân tàu cao cấp được chế tạo để bắt sinh vật đáy biển. Phù hợp để câu cá ở vùng &lt;color=#e7a60b&gt;Abyssal&lt;/color&gt;, tăng cơ hội thu được mẻ cá chất lượng cao.
+          <t>Một thân tàu cao cấp được chế tạo để bắt sinh vật đáy biển. Phù hợp để câu cá ở vùng &lt;color=#e7a60b&gt;Vực Sâu&lt;/color&gt;, tăng cơ hội thu được mẻ cá chất lượng cao.
 &lt;color=#929292&gt;Được trang bị bẫy ánh sáng và dây câu siêu dài, giúp bạn bắt được những con cá từ vực sâu thực sự.&lt;/color&gt;</t>
         </is>
       </c>
@@ -21770,8 +21769,8 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Một bong bóng kỳ bí đến từ quần đảo Riccioli. Được trang bị để mở khóa thiết bị &lt;color=#e7a60b&gt;Wonder Bubble&lt;/color&gt;, có sẵn để mua từ Planck. Sau khi mua, một Wonder Bubble sẽ xuất hiện tại bến tàu hiện tại của bạn để kích hoạt chế độ câu cá tự động (điều khiển Rachel tương tác với Bong Bóng để thu hoạch chiến lợi phẩm). 
-&lt;color=#929292&gt;Wonder Bubbles trôi nổi có thể chứa đủ loại hải sản từ biển cả.&lt;/color&gt;</t>
+          <t>Một bong bóng kỳ bí đến từ quần đảo Riccioli. Được trang bị để mở khóa thiết bị &lt;color=#e7a60b&gt;Bong Bóng Kỳ Diệu&lt;/color&gt;, có sẵn để mua từ Planck. Sau khi mua, một Bong Bóng Kỳ Diệu sẽ xuất hiện tại bến tàu hiện tại của bạn để kích hoạt chế độ câu cá tự động (điều khiển Rachel tương tác với Bong Bóng để thu hoạch chiến lợi phẩm). 
+&lt;color=#929292&gt;Những Bong Bóng Kỳ Diệu trôi nổi có thể chứa đủ loại hải sản từ biển cả.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21836,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Wonder Bubble chứa đựng bao điều kỳ diệu! Giờ đây, &lt;color=#e7a60b&gt;Wonder Bubble&lt;/color&gt; có thể thu hút những loài sinh vật biển quý hiếm hơn.
+          <t>Bong Bóng Kỳ Diệu chứa đựng bao điều kỳ diệu! Giờ đây, &lt;color=#e7a60b&gt;Bong Bóng Kỳ Diệu&lt;/color&gt; có thể thu hút những loài sinh vật biển quý hiếm hơn.
 &lt;color=#929292&gt;Nhiều sinh vật biển kỳ lạ đã bị cuốn vào bong bóng này... cho đến khi nó vỡ tan.&lt;/color&gt;</t>
         </is>
       </c>
@@ -22438,7 +22437,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Một khoang hình ống được lắp đặt trên tàu để phóng "Sweet Puffs". Thiết bị này có khả năng kích hoạt &lt;color=#e7a60b&gt;Bampuff&lt;/color&gt; để quét sạch tất cả Fishing Spots Cá trong phạm vi nhất định và mang về ngay kho báu cho bạn. (Có thể trang bị qua bánh xe Công cụ khi đi thuyền. Sử dụng sẽ tiêu hao "Sweet Puffs", có thể chuyển đổi từ Bampuffs.)
+          <t>Một khoang hình ống được lắp đặt trên tàu để phóng "Sweet Puffs". Thiết bị này có khả năng kích hoạt &lt;color=#e7a60b&gt;Bampuff&lt;/color&gt; để quét sạch tất cả Điểm Câu Cá trong phạm vi nhất định và mang về ngay kho báu cho bạn. (Có thể trang bị qua bánh xe Tiện Ích khi đi thuyền. Sử dụng sẽ tiêu hao "Sweet Puffs", có thể chuyển đổi từ Bampuffs.)
 &lt;color=#929292&gt;Bampuffs có sức nổ cực mạnh và nguy hiểm—cho cả tàu lẫn chiến lợi phẩm.&lt;/color&gt;</t>
         </is>
       </c>
@@ -22639,7 +22638,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Mồi câu truyền thống ở quần đảo Riccioli. Gắn vào để mở khóa &lt;color=#e7a60b&gt;Câu Mồi&lt;/color&gt;, tạo Điểm Fishing mang lại số lượng và chất lượng sinh vật biển cao hơn so với những gì bạn từng bắt được trong khu vực. (Có thể gắn qua bánh xe Công cụ khi đi thuyền. Sử dụng sẽ tiêu hao "Giun Cát", có thể mua tại cửa hàng bến tàu.)
+          <t>Mồi câu truyền thống ở quần đảo Riccioli. Gắn vào để mở khóa &lt;color=#e7a60b&gt;Câu Mồi&lt;/color&gt;, tạo Điểm Câu Cá mang lại số lượng và chất lượng sinh vật biển cao hơn so với những gì bạn từng bắt được trong khu vực. (Có thể gắn qua bánh xe Tiện ích khi đi thuyền. Sử dụng sẽ tiêu hao "Giun Cát", có thể mua tại cửa hàng bến tàu.)
 &lt;color=#929292&gt;Được chế tạo theo công thức cổ xưa của Riccioli, loại mồi này cực kỳ hiệu quả. Nhưng đừng hỏi bên trong có gì.&lt;/color&gt;</t>
         </is>
       </c>
@@ -22979,7 +22978,7 @@
           <t>Một cuốn sổ tay học sinh cũ kỹ, gáy sách sờn rách, chỉ còn sót lại vài mẩu thông tin.
 Chào mừng đến với Avinoleum. Cuốn sổ này sẽ là người hướng dẫn cho các học viên mới.
 1. Học viện gồm ba tòa tháp. Ngoài các phòng học dùng cho bài giảng hàng ngày, một tòa tháp được dành riêng cho các buổi tụ họp và sự kiện xã hội của học sinh. Tòa tháp này còn trưng bày chân dung của các Primus tiền nhiệm. Cả học sinh mới lẫn cũ đều có thể đến thăm và bày tỏ lòng kính trọng. Sau đó, mọi người phải rời đi theo trật tự.
-2. Đài quan sát và vườn hoa chỉ được phép lui tới trước giờ giới nghiêm. Ngoài khung giờ này, cấm vào. Student tuyệt đối không được cho rồng ăn. Ai vi phạm sẽ bị giam giữ từ ba đến năm ngày.</t>
+2. Đài quan sát và vườn hoa chỉ được phép lui tới trước giờ giới nghiêm. Ngoài khung giờ này, cấm vào. Học sinh tuyệt đối không được cho rồng ăn. Ai vi phạm sẽ bị giam giữ từ ba đến năm ngày.</t>
         </is>
       </c>
     </row>
@@ -23046,8 +23045,8 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>3. Học viên hoàn thành khóa huấn luyện hiệp sĩ có thể đăng ký tham gia kỳ thử thách. Hồ sơ phải nộp kèm tài liệu cần thiết trước ít nhất bảy ngày. Sau đó sẽ trải qua quá trình xét duyệt, trong đó giảng viên sẽ kiểm tra ứng viên không mang theo vũ khí hoặc Echoes cấm trước khi bước vào thử thách.
-4. Path Ban Phước chỉ mở cửa cho giảng viên và học viên trong lễ tế thần và Carnevale. Ngoài Carnevale, học viên được mời tham dự lễ tế thần phải mặc trang phục quy định và có thành viên của Dòng hộ tống đến Path Ban Phước để học tập.
+          <t>3. Học viên hoàn thành khóa huấn luyện hiệp sĩ có thể đăng ký tham gia kỳ thử thách. Hồ sơ phải nộp kèm tài liệu cần thiết trước ít nhất bảy ngày. Sau đó sẽ trải qua quá trình xét duyệt, trong đó giảng viên sẽ kiểm tra ứng viên không mang theo vũ khí hoặc Echo cấm trước khi bước vào thử thách.
+4. Con đường Ban Phước chỉ mở cửa cho giảng viên và học viên trong lễ tế thần và Carnevale. Ngoài Carnevale, học viên được mời tham dự lễ tế thần phải mặc trang phục quy định và có thành viên của Dòng hộ tống đến Con đường Ban Phước để học tập.
 Nhân danh Người Canh Gác trên cao, nguyện mọi học viên tìm thấy sự khai sáng tại Avinoleum.</t>
         </is>
       </c>
@@ -23117,7 +23116,7 @@
         <is>
           <t>Một cuốn nhật ký do thành viên Fisalia mang theo, ghi chép những nguyên tắc và điều cấm kỵ mà tất cả phải tuân theo.
 Về Gia tộc: Đừng tin tưởng mù quáng, kể cả người thân. Là một Fisalia, phước lành và sự bảo vệ phải do chính tay bạn kiếm lấy. Nếu chứng tỏ được giá trị, gia tộc sẽ cho phép bạn dùng mọi thủ đoạn để vươn lên. Ngay cả vị trí tộc trưởng cũng là báu vật có thể giành lấy với giá phải chăng. Phản bội là công cụ, tham lam là đức hạnh. Nhưng hãy nhớ, luôn sử dụng chúng một cách khéo léo.
-Về Việc Thăm viếng: Mọi lần đến dinh thự đều phải có lý do chính đáng. Với kẻ dám xâm nhập mà không được mời, nhà Fisalia sẽ cho họ nếm thử "lòng hiếu khách" theo cách của Fisalia. "Invite" họ ra đi, hoặc "mời" họ ở lại vĩnh viễn như một lời cảnh cáo cho kẻ khác. Khi lời mời được đưa ra, khách phải cư xử đúng mực và giữ kín miệng. Đừng để tò mò hay sợ hãi dẫn đến diệt vong.</t>
+Về Việc Thăm viếng: Mọi lần đến dinh thự đều phải có lý do chính đáng. Với kẻ dám xâm nhập mà không được mời, nhà Fisalia sẽ cho họ nếm thử "lòng hiếu khách" theo cách của Fisalia. "Mời" họ ra đi, hoặc "mời" họ ở lại vĩnh viễn như một lời cảnh cáo cho kẻ khác. Khi lời mời được đưa ra, khách phải cư xử đúng mực và giữ kín miệng. Đừng để tò mò hay sợ hãi dẫn đến diệt vong.</t>
         </is>
       </c>
     </row>
@@ -23388,7 +23387,7 @@
       <c r="M338" t="inlineStr">
         <is>
           <t>Cái vạc mà Cantarella, Phù Thủy Biển, dùng để nấu thuốc tiên. Viên ngọc sapphire gắn trên đó tượng trưng cho quyền lực của bà với tư cách thủ lĩnh tộc Fisalias.
-Bà thường để cảm hứng dẫn dắt, bất cẩn Dodgem vào những nguyên liệu kỳ lạ như xúc tu sứa, vảy cá, nước mắt của kẻ thất tình, thậm chí cả những lời thì thầm vương vấn trong gió.
+Bà thường để cảm hứng dẫn dắt, bất cẩn ném vào những nguyên liệu kỳ lạ như xúc tu sứa, vảy cá, nước mắt của kẻ thất tình, thậm chí cả những lời thì thầm vương vấn trong gió.
 Dù cho bà thêm gì đi nữa, kết quả luôn là một nồi mộng đẹp ngọt ngào, xoa dịu nỗi đắng cay của thực tại, vỗ về những tâm hồn lạc lối trong vực sâu.</t>
         </is>
       </c>
@@ -23469,8 +23468,8 @@
 "Hôm nay ta mời mọi người đến đây để bàn một việc: chúng ta nên ở lại đâu? Trong '&lt;te href=850119&gt;Giấc Mơ Ảo Ảnh&lt;/te&gt;', hay trở về thực tại?" 
 "Chúng ta đã lang thang nơi ranh giới của những giấc mơ, vậy nên ở lại đây, trong ảo ảnh này, nơi mọi thứ quen thuộc, nhẹ nhàng như bong bóng? Hay bước về phía trước, vào thực tại, nơi ta có thể đối mặt với những điều chưa biết… nhưng cũng được thấy những cảnh tượng chưa từng biết đến?" 
 Một giọng nói uể oải nhưng kiên quyết cắt ngang lời cô. "Yếu đuối quá, Cantarella. Giờ ngươi là người đứng đầu gia tộc, nhưng theo ta thấy, ngươi còn lâu mới đủ khả năng." 
-Một bóng người bước ra từ bóng tối, một người phụ nữ với mái tóc dài như thác nước. Cô đeo chiếc mặt dây chuyền sapphire giống Cantarella và mang dáng vẻ thanh nhã tương tự, nhưng lại toát lên sự từng trải và uy quyền không thể chối cãi. Đôi mắt tím sẫm của cô lóe lên vẻ sắc bén không thể nhầm lẫn. 
-"Buổi họp này vô nghĩa. Chỉ cần đổ '&lt;te href=850120&gt;Velvet Dream&lt;/te&gt;' xuống thác nước sau lâu đài, cả &lt;te href=850097&gt;Ragunna&lt;/te&gt; sẽ chìm vào giấc mơ dưới sự kiểm soát của ngươi. Như vậy, dù đi đâu, chúng ta cũng sẽ là nữ hoàng." 
+Một bóng người bước ra từ bóng tối, một người phụ nữ với mái tóc dài như thác nước. Cô đeo chiếc mặt dây chuyền sapphire giống Cantarella và mang dáng vẻ thanh tao tương tự, nhưng lại toát lên sự từng trải và uy quyền không thể chối cãi. Đôi mắt tím sẫm của cô lóe lên vẻ sắc bén không thể nhầm lẫn. 
+"Buổi họp này vô nghĩa. Chỉ cần đổ '&lt;te href=850120&gt;Giấc Mơ Nhung&lt;/te&gt;' xuống thác nước sau lâu đài, cả &lt;te href=850097&gt;Ragunna&lt;/te&gt; sẽ chìm vào giấc mơ dưới sự kiểm soát của ngươi. Như vậy, dù đi đâu, chúng ta cũng sẽ là nữ hoàng." 
 "Câu trả lời không hợp lệ. Hoặc nếu chị nhất quyết, em sẽ tính là một phiếu cho 'Giấc Mơ Ảo Ảnh'. Tuy nghe có vẻ hoang đường và thiếu thực tế, nhưng em vẫn sẽ ghi lại cho công bằng. Đây là buổi thảo luận của chúng ta mà." Một cô gái trẻ ngồi bên cạnh lên tiếng, mở cuốn sổ đầy những hình vẽ kỳ lạ. Cô tìm một khoảng trống nhỏ gần như bị chôn vùi dưới công thức pha chế thuốc và nghiêm túc kẻ một đường thẳng tắp. 
 "Em bỏ phiếu trắng," cô nói thoải mái. "Cuộc thảo luận này có lẽ chẳng thay đổi được gì đâu. Chị đã có câu trả lời của riêng mình rồi, phải không? Còn với em, ở đâu cũng được." Cô đóng sổ lại với một tiếng bật nhẹ và phủi chiếc khăn choàng trắng. Ánh sáng bắt lấy đôi mắt xanh mờ ảo của cô. 
 "Sao chúng ta không đơn giản là làm theo trái tim mình nhỉ? Cantarella, chị thích ngắm đàn chim ngoài cửa sổ và khao khát cuộc sống tự do, phải không? Vậy thì cứ làm điều chị thấy đúng thôi," cô bé nhỏ tuổi nhất nói, nằm dài trên ghế sofa, tay lơ đãng đuổi theo những hạt bụi nhảy múa trong ánh sáng. 
@@ -23551,7 +23550,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Vương miện gai độc màu tím thẫm, khi mới đội lên trán, mang lại một cơn đau nhói. Nhưng máu chảy ra từ vết thương lại nuôi dưỡng nó, khiến nó càng sáng rực rỡ hơn. Ngấm đẫm máu và nước mắt của vô số linh hồn, chiếc vương miện gai độc này vươn lên từ đáy biển sâu, tượng trưng cho những kẻ âm thầm chống lại hỗn loạn để gánh vác sức nặng của đuôi lông vũ Celestial Steed.
+          <t>Vương miện gai độc màu tím thẫm, khi mới đội lên trán, mang lại một cơn đau nhói. Nhưng máu chảy ra từ vết thương lại nuôi dưỡng nó, khiến nó càng sáng rực rỡ hơn. Ngấm đẫm máu và nước mắt của vô số linh hồn, chiếc vương miện gai độc này vươn lên từ đáy biển sâu, tượng trưng cho những kẻ âm thầm chống lại hỗn loạn để gánh vác sức nặng của đuôi lông vũ Thiên Mã.
 Đó chính là vinh quang của gia tộc &lt;te href=850094&gt;Fisalia&lt;/te&gt;, và số phận không thể trốn thoát của họ.
 Nhưng từng thành viên trong gia tộc thì sao? Trong bóng tối biển sâu, họ phải chịu đựng những lời thì thầm gặm nhấm tâm can, cho đến khi tia hy vọng cuối cùng về niềm tin chân chính trong tim họ cũng lụi tàn, chìm vào vực thẳm. Người kế vị sẽ đội lên vương miện, tiếp nối nghĩa vụ, và vòng luân hồi ấy kéo dài bất tận, không đầu không cuối.
 Những đóa hoa thơm mà độc,
@@ -23561,9 +23560,9 @@
 Độc tố sinh học,
 Độc tố kim loại…
 Những chất độc và độc tố mà gia tộc Fisalia tự hào, cùng những năng lực sinh ra từ chúng, rốt cuộc cũng sẽ bị những lời thì thầm ấy phá hủy… Cuối cùng, chúng chỉ hữu dụng khi được dùng để tìm đến cái chết, cho chính họ hoặc cho người thân.
-Điều này đã là lẽ thường từ lâu, cho đến khi ta phát triển "&lt;te href=850119&gt;Illusory Dream Ảnh&lt;/te&gt;." Khi vương miện gai cắm vào da thịt ta, máu chảy ra với những sắc màu lấp lánh kỳ lạ. Trà đen pha thủy ngân bỗng có vị ngọt ngào như mật ong, còn bánh nướng ngâm nước ép Hoa Thạch Tùng mang vị ngọt thanh dịu. Cảm giác nóng rát trong cổ họng như nuốt vội một quả anh đào, còn cảm giác ngột ngạt như trôi dạt giữa biển cả vô tận… Dần dần, cơn đau tan biến, cả thân xác lẫn tâm trí đều nhẹ bẫng. Những lọ chất độc vỡ tan trên sàn, Dodget mặt chúng ta trở nên nhẹ nhõm. Những lời thì thầm trở nên bất lực trong thế giới được dệt nên từ biển mộng, bởi nó nhẹ nhàng hòa tan mọi bất hòa. Giữa những con sóng đầy màu sắc, vương miện gai độc từng sắc nhọn giờ đây trở nên mềm mại… Mềm mại đến mức tạo thành những nếp gấp nhẹ nhàng, chỉ còn khẽ đặt trên đầu ta. Nó trở nên nhẹ nhàng và thuần khiết, như những chiếc lông vũ đuôi của Celestial Steed.
-Đó là lý do ta bỏ phiếu cho "Illusory Dream Ảnh." Dù sao, ảo ảnh này có hại gì đâu? Chẳng phải tất cả chúng ta đã lang thang ở đây quá lâu rồi sao? Hãy đổ "&lt;te href=850120&gt;Giấc Mộng Nhung&lt;/te&gt;" vào thác nước sau lâu đài, để cả &lt;te href=850097&gt;Ragunna&lt;/te&gt; chìm vào giấc mộng do ta tạo nên… Yên tâm đi, đây chỉ là trò đùa thôi. Ta không muốn kiểm soát ai, chỉ mong mọi người được sống yên bình hơn mà thôi.
-Các ngươi thấy đấy, "Illusory Dream Ảnh" đã chảy trong huyết quản chúng ta, dù muốn hay không, nó đã trở thành một phần vĩnh viễn và không thể tách rời.</t>
+Điều này đã là lẽ thường từ lâu, cho đến khi ta phát triển "&lt;te href=850119&gt;Giấc Mộng Ảo Ảnh&lt;/te&gt;." Khi vương miện gai cắm vào da thịt ta, máu chảy ra với những sắc màu lấp lánh kỳ lạ. Trà đen pha thủy ngân bỗng có vị ngọt ngào như mật ong, còn bánh nướng ngâm nước ép Hoa Thạch Tùng mang vị ngọt thanh dịu. Cảm giác nóng rát trong cổ họng như nuốt vội một quả anh đào, còn cảm giác ngột ngạt như trôi dạt giữa biển cả vô tận… Dần dần, cơn đau tan biến, cả thân xác lẫn tâm trí đều nhẹ bẫng. Những lọ chất độc vỡ tan trên sàn, nét mặt chúng ta trở nên nhẹ nhõm. Những lời thì thầm trở nên bất lực trong thế giới được dệt nên từ biển mộng, bởi nó nhẹ nhàng hòa tan mọi bất hòa. Giữa những con sóng đầy màu sắc, vương miện gai độc từng sắc nhọn giờ đây trở nên mềm mại… Mềm mại đến mức tạo thành những nếp gấp nhẹ nhàng, chỉ còn khẽ đặt trên đầu ta. Nó trở nên nhẹ nhàng và thuần khiết, như những chiếc lông vũ đuôi của Thiên Mã.
+Đó là lý do ta bỏ phiếu cho "Giấc Mộng Ảo Ảnh." Dù sao, ảo ảnh này có hại gì đâu? Chẳng phải tất cả chúng ta đã lang thang ở đây quá lâu rồi sao? Hãy đổ "&lt;te href=850120&gt;Giấc Mộng Nhung&lt;/te&gt;" vào thác nước sau lâu đài, để cả &lt;te href=850097&gt;Ragunna&lt;/te&gt; chìm vào giấc mộng do ta tạo nên… Yên tâm đi, đây chỉ là trò đùa thôi. Ta không muốn kiểm soát ai, chỉ mong mọi người được sống yên bình hơn mà thôi.
+Các ngươi thấy đấy, "Giấc Mộng Ảo Ảnh" đã chảy trong huyết quản chúng ta, dù muốn hay không, nó đã trở thành một phần vĩnh viễn và không thể tách rời.</t>
         </is>
       </c>
     </row>
@@ -23639,18 +23638,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Trong căn phòng mờ tối nặng mùi hương kỳ lạ, ánh sáng vàng nhạt chiếu lên một cuốn sổ cũ và chiếc vạc kỳ dị. Người phụ nữ trẻ khoác chiếc khăn choàng trắng, vừa ghi chép vào sổ vừa thả nguyên liệu vào vạc một cách thoải mái. Khói bốc lên từ đó làm đen quần áo cô, để lại những mảng màu đen và tím. Tấm tạp dề từng sạch sẽ giờ đây lấm lem, nhưng cô chỉ lau mặt qua loa, không màng đến sự bừa bộn.
-Nước cất, bạc hà, hạt thầu dầu, lá cá vảy hàu, hương thảo… Mùi hương tươi mát, độc tính nhẹ, có tác dụng an thần và giảm đau. Có thể dùng để điều trị hội chứng Vật Chất Xám ở trẻ em thường thấy gần đây… Tôi sẽ ghi công thức này vào một mảnh giấy nhỏ và để lại cho Chloe sau.
-Cỏ Hilo, đậu biển, lá cá vảy hàu, nước ép táo biển… Mùi khó chịu, độc tính mạnh, nhưng có thể trung hòa một số phản ứng tê liệt thần kinh. Hmm, nhưng tác dụng phụ… Thôi kệ, tôi sẽ giữ lại.
-Chất nhầy đậu biển, lá cá vảy hàu phơi khô và nghiền nhỏ, một chút nước ép táo biển, thêm một ít nước ép Jellyrose… Độc tính của Jellyrose quá mạnh. Hiệu quả, nhưng quá mạo hiểm.
-Nghiền lá cá vảy hàu, rưới nước ép Violacas, trộn với chất nhầy đậu biển, thêm một chút nước ép táo biển, rồi để lên men trong lọ thủy tinh… Done. Uống vào sẽ trấn tĩnh tinh thần và trung hòa hầu hết phản ứng ngộ độc. Tôi nên phát một ít cho mọi người để vượt qua những thử thách trong những ngày tới. Còn tên gọi… được rồi, tôi sẽ đặt là &lt;te href=850120&gt;Velvet Dream&lt;/te&gt;.
-Nguyên liệu, phương pháp chế biến, trình tự chuẩn bị và nhiệt độ môi trường… Xử lý từng bước vào đúng thời điểm, và tôi có thể pha chế ra loại thuốc hoàn hảo. Tôi tin điều này cũng áp dụng được cho cuộc sống. Vào đúng thời điểm, với những bước đi đúng đắn, hầu hết vấn đề đều có thể giải quyết. Dù quy tắc có phi lý hay tình huống có khắc nghiệt đến đâu, luôn có cách để tìm ra phương pháp đúng đắn.
-Vì vậy, tôi bước vào bóng tối với ngọn đèn, đối mặt với nỗi sợ hãi của mình. Vực thẳm chế nhạo tôi—ẩn dật, yếu đuối, không thể thích nghi. Những tiếng cười nhạo vang vọng qua các hành lang, những tần số méo mó của các gia trưởng quá khứ ùa về, nhấn chìm tôi. Nghiêm nghị, cứng nhắc, nhợt nhạt, u ám, im lặng… Họ hiểu tôi quá rõ, có thể đoán trước từng động thái và bẫy tôi một cách dễ dàng.
-Nhưng dù sao, tôi vẫn thực hiện trò lừa đầu tiên và cũng là cuối cùng của mình khi uống trước một liều lớn Velvet Dream. Khi những chiếc gai độc của sứa đâm xuyên da tôi, tôi ấn Medusa Jellyrose lên đầu. Những chất độc dữ dội va chạm trong huyết quản, suýt xé nát tôi. Linh hồn tôi lơ lửng giữa sự sống và cái chết, trên bờ vực trào ra khỏi cổ họng đang cháy bỏng. Tôi không biết đó là máu, nước mắt hay mồ hôi hòa lẫn với tàn dư của thuốc… Nó nhỏ giọt lên ngọn đèn gần tắt.
-Một con sứa nhỏ lảo đảo bước ra từ ánh sáng le lói. Khi tôi ngẩng mắt lên, bóng tối tan biến, và tầm nhìn mờ ảo của tôi tràn ngập những ảo giác đầy màu sắc, sống động.
-It worked.
-Vậy đấy, như tôi đã nói, bất kỳ tình huống nào cũng có thể giải quyết bằng những bước đi đúng đắn vào đúng thời điểm, ngay cả khi bạn chỉ là một phần của quá trình. Kể từ đó, tôi luôn ở trong trạng thái lơ lửng giữa sự sống và cái chết, giữa giấc mơ và thực tại. Tôi thường bắt gặp những ảo giác thoáng qua, như cô gái đội mũ đỏ. Who is she? Là tôi? Hay một ai khác? Tôi không thể phân biệt được.
-Dù sao đi nữa, tôi sẽ không tham gia bỏ phiếu. Dù là trong mơ hay thực tại, tôi đã quen rồi, và tôi có thể sống sót ở bất cứ đâu.</t>
+          <t>Trong căn phòng mờ tối, nặng mùi hương kỳ lạ, ánh đèn vàng nhạt rọi lên một cuốn sổ cũ và chiếc vạc kỳ quái. Người phụ nữ trẻ khoác tấm khăn choàng trắng, hí hoáy ghi chép vào cuốn sổ trong khi thản nhiên ném nguyên liệu vào vạc. Khói bốc lên nhuộm đen quần áo cô, để lại những vệt tím đen loang lổ. Tấm tạp dề từng trắng tinh giờ đây lấm lem, nhưng cô chỉ thản nhiên lau mặt, chẳng màng đến vẻ bừa bộn.</t>
         </is>
       </c>
     </row>
@@ -25316,10 +25304,10 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Angry Listener: Đồ thoái hóa! Đồ đạo đức giả kiêu ngạo, tất cả bọn ngươi! Mấy người có biết chuyện gì đã xảy ra không... chẳng biết gì cả!
-Angry Listener: Liệu Hội đã biến những hy sinh của chúng ta thành những câu chuyện kể bên tách trà sao? Phước lành của Sentinel. Thật nực cười!
-Angry Listener: Các người đã ở đâu khi chúng ta chiến đấu với lũ Tacet Discord tại Whisperwind Haven? Các người đã ở đâu? Sentinel đã ở đâu?!
-Angry Listener: Chúng ta không chiến đấu vì Sentinel hay cái Hội该死 ấy. Chúng ta chiến đấu vì chính mình! Đồ đạo đức giả!</t>
+          <t>Thính Giả Giận Dữ: Đồ thoái hóa! Đồ đạo đức giả kiêu ngạo, tất cả bọn mày! Mấy người có biết chuyện gì đã xảy ra không... chẳng biết gì cả!
+Thính Giả Giận Dữ: Liệu Hội đã biến những hy sinh của chúng ta thành những câu chuyện kể bên tách trà sao? Phước lành của Sentinel. Thật nực cười!
+Thính Giả Giận Dữ: Các người đã ở đâu khi chúng ta chiến đấu với lũ Tacet Discord tại Whisperwind Haven? Các người đã ở đâu? Sentinel đã ở đâu?!
+Thính Giả Giận Dữ: Chúng ta không chiến đấu vì Sentinel hay cái Hội该死 ấy. Chúng ta chiến đấu vì chính mình! Đồ đạo đức giả!</t>
         </is>
       </c>
     </row>
@@ -25453,9 +25441,9 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>"Girl trong Thư phòng": Trà chiều! Vâng, con xin!
+          <t>"Cô gái trong Thư phòng": Trà chiều! Vâng, con xin!
 Hầu gái: Trà và bánh quy của cô đây. Sau khi dùng xong, tôi sẽ bôi thuốc lại cho cô. Lần sau không được leo tường nữa, hiểu chưa?
-"Girl trong Thư phòng": Đâu phải con leo cho vui, con đang cố—</t>
+"Cô gái trong Thư phòng": Đâu phải con leo cho vui, con đang cố—</t>
         </is>
       </c>
     </row>
@@ -25521,8 +25509,8 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Maid: Thôi nào, thôi nào. Con vốn là đứa trẻ tò mò mà. Con thấy thứ gì đó thú vị nên mới lẻn ra xem cho rõ.
-"Cô Gái Trong Phòng Nghiên Cứu": Mmmff... Khoan, đợi đã! Có phải mâm xôi không? Món con thích nhất. Hả? Á... đau, đau quá!</t>
+          <t>Hầu Gái: Thôi nào, thôi nào. Con vốn là đứa trẻ tò mò mà. Con thấy thứ gì đó thú vị nên mới lẻn ra xem cho rõ.
+"Cô Gái Trong Phòng Nghiên Cứu": Mmmff... Đợi đã, đợi đã! Có phải mâm xôi không? Món con thích nhất. Hả? Á... đau, đau quá!</t>
         </is>
       </c>
     </row>
@@ -25588,8 +25576,8 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>"Girl trong Thư phòng": Nhìn này! Cuốn sách này bảo loài hoa này không sống lâu, thật ngớ ngẩn. Con biết nó có thể sống qua mùa đông lạnh giá nhất!
-"Girl trong Thư phòng": Rồi một ngày, con sẽ trở thành một nghệ sĩ hát rong vĩ đại. Một người &lt;i&gt;đích thực&lt;/i&gt;, không bao giờ mắc lỗi như thế này!</t>
+          <t>"Cô gái trong Thư phòng": Nhìn này! Cuốn sách này bảo loài hoa này không sống lâu, thật ngớ ngẩn. Con biết nó có thể sống qua mùa đông lạnh giá nhất!
+"Cô gái trong Thư phòng": Rồi một ngày, con sẽ trở thành một nghệ sĩ hát rong vĩ đại. Một người &lt;i&gt;đích thực&lt;/i&gt;, không bao giờ mắc lỗi như thế này!</t>
         </is>
       </c>
     </row>
@@ -25656,9 +25644,9 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Maid: Tiểu thư, căn phòng nghiên cứu này là bí mật... Tiểu thư không được tiết lộ cho bất kỳ ai đâu nhé.
+          <t>Hầu Gái: Tiểu thư, căn phòng nghiên cứu này là bí mật... Tiểu thư không được tiết lộ cho bất kỳ ai đâu nhé.
 "Cô Gái Trong Phòng Nghiên Cứu": Con hiểu rồi, nhưng con vẫn luôn thắc mắc... Tại sao mọi người lại nói họ có tội? Ở đây có biết bao bài thơ và khúc ca hay ho. Tại sao cha lại không cho con xem chúng nhỉ?
-Maid: Ồ, sau này lớn lên tiểu thư sẽ hiểu thôi...</t>
+Hầu Gái: Ồ, sau này lớn lên tiểu thư sẽ hiểu thôi...</t>
         </is>
       </c>
     </row>
@@ -25726,7 +25714,7 @@
       <c r="M372" t="inlineStr">
         <is>
           <t>Các thi nhân đã thực sự lên con tàu Pilgrim's Sail, trở thành những vì sao trong màn cuối của chính mình.
-Ta đều biết kết cục của câu chuyện ấy—ngọn lửa lớn đã thiêu rụi con tàu, kéo nó xuống vực băng giá, cùng với những thi nhân của Golden Anthem.
+Ta đều biết kết cục của câu chuyện ấy—ngọn lửa lớn đã thiêu rụi con tàu, kéo nó xuống vực băng giá, cùng với những thi nhân của Khúc Ca Hoàng Kim.
 Nhưng hãy nghe đây, lưu đày không gieo mầm hận thù trong lòng họ với thành phố này, và ngọn lửa không thiêu đốt lời nguyền vào nhạc khúc hay thơ ca của họ.</t>
         </is>
       </c>
@@ -25794,8 +25782,8 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Nếu muốn nghe lại giọng hát chân thật của họ, hãy tìm đến Cathedral of Mercury.
-Những đứa trẻ ở đó vẫn hát những bài thánh ca do các thi nhân của Golden Anthem viết, thế nhưng... không một Daemon nào xuất hiện.
+          <t>Nếu muốn nghe lại giọng hát chân thật của họ, hãy tìm đến Nhà Thờ Mercury.
+Những đứa trẻ ở đó vẫn hát những bài thánh ca do các thi nhân của Khúc Ca Hoàng Kim viết, thế nhưng... không một Daemon nào xuất hiện.
 Ngay cả khi những thi nhân đó đã đối mặt với cái chết—</t>
         </is>
       </c>
@@ -26535,9 +26523,9 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Hội Thi Nhân và gia tộc ta không bao giờ chứng minh được hình dạng của Sentinel có thực sự là một Celestial Steed hay không.
+          <t>Hội Thi Nhân và gia tộc ta không bao giờ chứng minh được hình dạng của Sentinel có thực sự là một Thiên Mã hay không.
 Tất cả những gì chúng ta làm được chỉ là giữ lấy những nghi ngờ và sự thật có thể... chờ đợi ai đó chứng minh.
-Giờ đây... người đó đã đến. {Male=Hắn;Female=Cô ấy} đã đặt chân đến tòa tháp đảo ngược.</t>
+Giờ đây... người đó đã đến. {Male=He;Female=She} đã đặt chân đến tòa tháp đảo ngược.</t>
         </is>
       </c>
     </row>
@@ -27011,7 +26999,7 @@
       <c r="M391" t="inlineStr">
         <is>
           <t>Điều đó không hợp lý lắm. 
-Nếu địa ngục lửa chỉ là thứ còn sót lại từ Pilgrim's Sail, vậy... liệu họ có thực sự muốn nguyền rủa Ragunna không?
+Nếu địa ngục lửa chỉ là thứ còn sót lại từ Cánh Buồm Hành Hương, vậy... liệu họ có thực sự muốn nguyền rủa Ragunna không?
 Nếu vậy... lẽ ra lời nguyền đã thành hiện thực rồi chứ?</t>
         </is>
       </c>
@@ -27215,7 +27203,7 @@
       <c r="M394" t="inlineStr">
         <is>
           <t>Không, chính Order và những kẻ khác đã "nguyền rủa" tác phẩm của họ, rồi cố tình phổ biến chúng như những "tác phẩm cấm" ra công chúng... 
-Nhưng why? Nếu mục đích của họ là bịt miệng cậu vì biết sự thật về Blessed Maiden và Imperator, thì đó quả là một nỗ lực vụng về.</t>
+Nhưng tại sao? Nếu mục đích của họ là bịt miệng cậu vì biết sự thật về Blessed Maiden và Imperator, thì đó quả là một nỗ lực vụng về.</t>
         </is>
       </c>
     </row>
@@ -27621,9 +27609,9 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Solo &amp; Co-op)
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
 Cơ hội hồi sinh chung: 9
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27690,9 +27678,9 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Solo &amp; Co-op)
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
 Cơ hội hồi sinh chung: 6
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27761,9 +27749,9 @@
       <c r="M402" t="inlineStr">
         <is>
           <t>Mỗi lần sẽ chọn ngẫu nhiên một trong năm thử thách.
-Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
+Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Đồng đội)
 Lượt hồi sinh chung: 4
-&lt;color=#aa9b6a&gt;Resonators thử nghiệm sẽ có sẵn trong chế độ Chơi đơn.&lt;/color&gt;</t>
+&lt;color=#aa9b6a&gt;Resonator thử nghiệm sẽ có sẵn trong chế độ Chơi đơn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27829,7 +27817,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Thành viên đội bảo vệ Averardo Vault và chủ nhân danh hiệu "Nhân Viên Xuất Sắc" lâu hơn cả thời gian cô muốn nhớ.
+          <t>Thành viên đội bảo vệ Hầm Averardo và chủ nhân danh hiệu "Nhân Viên Xuất Sắc" lâu hơn cả thời gian cô muốn nhớ.
 Cô đã lên vô số kế hoạch cho thời gian rảnh, nhưng hiện tại, nhiệm vụ lớn nhất của cô đơn giản thôi: tan ca đúng giờ.</t>
         </is>
       </c>
@@ -30050,7 +30038,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Định mệnh Dodgem một viên đá xuống dòng sông thời gian, và từng gợn sóng sẽ khắc ghi con đường ta đi qua số phận. {0}-{1}-{2}—trong ngày bình thường mà đặc biệt này, quá khứ, hiện tại và tương lai của ngươi giao nhau trong khoảnh khắc ngắn ngủi. Và giờ đây, &lt;color=#fa601a&gt;ai đang đứng trước mặt ngươi?&lt;/color&gt;</t>
+          <t>Định mệnh ném một viên đá xuống dòng sông thời gian, và từng gợn sóng sẽ khắc ghi con đường ta đi qua số phận. {0}-{1}-{2}—trong ngày bình thường mà đặc biệt này, quá khứ, hiện tại và tương lai của ngươi giao nhau trong khoảnh khắc ngắn ngủi. Và giờ đây, &lt;color=#fa601a&gt;ai đang đứng trước mặt ngươi?&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30976,7 +30964,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Ánh sao rơi xuống biển sâu, lấp đầy khát khao và trống rỗng trong lòng nàng. Trong sự bao la và cô độc, nàng vẫn đứng canh gác những bờ biển chỉ tồn tại vì {Male=anh;Female=cô}... Đó là bổn phận từ trong máu thịt, của quá khứ và tương lai.</t>
+          <t>Ánh sao rơi xuống biển sâu, lấp đầy khát khao và trống rỗng trong lòng nàng. Trong sự bao la và cô độc, nàng vẫn đứng canh gác những bờ biển chỉ tồn tại vì {Male=him;Female=her}... Đó là bổn phận từ trong máu thịt, của quá khứ và tương lai.</t>
         </is>
       </c>
     </row>
@@ -31303,7 +31291,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Giương buồm lên! Màn diễn bắt đầu! Sân khấu biển cả này là của Brant. Từ mũi tàu thoảng hương "Strength Đoàn Hội" cùng tiếng cười ngạo nghễ chế giễu những giáo điều lỗi thời của The Order. Trên boong, họ đang diễn lại những vở kịch bị The Order cấm. Từ đuôi tàu, biển cả đuổi theo như thể truy bắt họ.</t>
+          <t>Giương buồm lên! Màn diễn bắt đầu! Sân khấu biển cả này là của Brant. Từ mũi tàu thoảng hương "Sức Mạnh Đoàn Hội" cùng tiếng cười ngạo nghễ chế giễu những giáo điều lỗi thời của The Order. Trên boong, họ đang diễn lại những vở kịch bị The Order cấm. Từ đuôi tàu, biển cả đuổi theo như thể truy bắt họ.</t>
         </is>
       </c>
     </row>
@@ -31632,7 +31620,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Điều biến là hành động Triển Khai một Echoes từ tay bạn lên trên một Echoes đã có trên chiến trường. Echoes mới Triển Khai sẽ kế thừa và kích hoạt tất cả Skills Special từ Echoes mà nó được đặt lên.</t>
+          <t>Điều biến là hành động Triển Khai một Echo từ tay bạn lên trên một Echo đã có trên chiến trường. Echo mới Triển Khai sẽ kế thừa và kích hoạt tất cả Kỹ Năng Đặc Biệt từ Echo mà nó được đặt lên.</t>
         </is>
       </c>
     </row>
@@ -31697,7 +31685,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Tiếng vọng có khả năng Biến Hình sẽ có hiệu lực khi được kéo vào Khu Biến Hình. Thông thường, các lá bài đã Biến Hình sẽ không được trả về bộ bài mà bị tiêu hủy trong trận đấu này.</t>
+          <t>Echo có khả năng Biến Hình sẽ có hiệu lực khi được kéo vào Khu Biến Hình. Thông thường, các lá bài đã Biến Hình sẽ không được trả về bộ bài mà bị tiêu hủy trong trận đấu này.</t>
         </is>
       </c>
     </row>
@@ -31764,9 +31752,9 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Điều Chỉnh giúp Echoes Activate những khả năng mạnh mẽ.
-- Skills Special sẽ ở trạng thái Chưa Activate khi Echoes mới được Triển Khai và cần được Activate.
-- Điều Chỉnh sẽ Activate Skills Special của Echoes được Điều Chỉnh.</t>
+          <t>Điều Chỉnh giúp Echo Kích Hoạt những khả năng mạnh mẽ.
+- Kỹ Năng Đặc Biệt sẽ ở trạng thái Chưa Kích Hoạt khi Echo mới được Triển Khai và cần được Kích Hoạt.
+- Điều Chỉnh sẽ Kích Hoạt Kỹ Năng Đặc Biệt của Echo được Điều Chỉnh.</t>
         </is>
       </c>
     </row>
@@ -31831,7 +31819,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Resilience&lt;/color&gt; - Lần đầu tiên Resonator này chịu đòn chí mạng trong Battle Stage, nó sẽ trụ lại thêm {0} giây trước khi bị hạ gục.</t>
+          <t>&lt;color=#e4c69b&gt;Kiên Cường&lt;/color&gt; - Lần đầu tiên Cộng Hưởng Giả này chịu đòn chí mạng trong Giai Đoạn Chiến Đấu, nó sẽ trụ lại thêm {0} giây trước khi bị hạ gục.</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32082,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Để thay đổi ngoại hình của Rover, bạn cần tài nguyên này. Hãy hoàn tất tải xuống trước khi chuyển đổi.
+          <t>Để thay đổi ngoại hình của Vận Mệnh Giả, bạn cần tài nguyên này. Hãy hoàn tất tải xuống trước khi chuyển đổi.
 Bạn có thể tiếp tục chơi trong lúc tải. Thông báo sẽ hiện ra khi tải xong.</t>
         </is>
       </c>
@@ -32160,7 +32148,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32225,7 +32213,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32290,7 +32278,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32355,7 +32343,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32408,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32485,7 +32473,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32550,7 +32538,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32615,7 +32603,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32680,7 +32668,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32745,7 +32733,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32810,7 +32798,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32875,7 +32863,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32940,7 +32928,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33005,7 +32993,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33070,7 +33058,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33135,7 +33123,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33200,7 +33188,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33265,7 +33253,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33330,7 +33318,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33395,7 +33383,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33460,7 +33448,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33525,7 +33513,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33590,7 +33578,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33655,7 +33643,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33720,7 +33708,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33773,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33850,7 +33838,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33915,7 +33903,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33980,7 +33968,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34045,7 +34033,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34110,7 +34098,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34175,7 +34163,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34240,7 +34228,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
